--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="11.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1357,6 +1357,5633 @@
       </c>
       <c r="K18" s="2" t="n">
         <v>2.3522</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>france-alzheimer-77</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>France Alzheimer Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Fargeau-Ponthierry</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15 Rue des Prés, 77310 Saint-Fargeau-Ponthierry</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>06 38 45 49 83</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/seineetmarne/</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Écoute, information et soutien aux aidants et familles de personnes atteintes de la maladie d'Alzheimer ou d'une maladie apparentée. Email : france-alzheimer77@orange.fr</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>48.5769</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2.6062</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>colombe-des-aidants-77</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>La Colombe des Aidants</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Héricy</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jeveuxaider.gouv.fr/organisations/22550-la-colombe-des-aidants</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Permanences d'écoute (Héricy, Champagne-sur-Seine, Chailly-en-Bière), groupes de parole "T'Aidant" et haltes-répit pour les aidants du Sud Seine-et-Marne.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>48.4453</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>2.7273</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>pfr-repit-avonnais-77</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Le Répit Avonnais</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Avon</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>44 Avenue de Valvins, Immeuble Odéon 44, 77210 Avon</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>01 60 57 01 60</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Soutien psychologique individuel et temps de répit pour les aidants. Ouvert du lundi au vendredi, 9h-17h.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>48.402</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2.7285</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>pfr-jardins-sedna-77</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Les Jardins de Sedna</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Avon</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue du Père Maurice, 77210 Avon</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>01 60 72 74 72</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Temps de répit et accompagnement pour les aidants.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>48.402</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2.7285</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>pfr-tournan-en-brie-77</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Établissement public gérontologique</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Tournan-en-Brie</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>99 Rue de Paris, 77220 Tournan-en-Brie</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>01 64 42 18 08</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour la personne malade et temps de répit pour l'aidant. Ouvert du lundi au vendredi, 9h30-17h.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>48.7304</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2.7725</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>pfr-ferte-sous-jouarre-77</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Le Nid des Aidants 77</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>La Ferté-sous-Jouarre</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>20 Boulevard du 8 Mai 1945, 77260 La Ferté-sous-Jouarre</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>01 78 81 12 12</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Dispositif itinérant sur le nord du département : séjours de répit, relayage à domicile, accueil de jour pour les aidants.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>48.9532</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>3.1258</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ligne-aidants-cd77</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ligne des Aidants — Département de Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Melun</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>77 — Seine-et-Marne</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>01 64 79 73 29</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Ligne d'écoute et d'orientation gratuite pour les aidants.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>48.5389</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>france-alzheimer-78</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>France Alzheimer Yvelines</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Versailles</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>01 39 50 03 86</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/yvelines/</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Groupes de parole et permanences d'écoute par secteur (Versailles, Saint-Germain-en-Laye, Saint-Quentin-en-Yvelines, Poissy, Conflans-Sainte-Honorine, Verneuil-sur-Seine, Cœur d'Yvelines). Email : contact78@francealzheimer.org</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>48.8049</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>2.1204</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>pfr-saint-joseph-78</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit Saint-Joseph Yvelines Nord-Est</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Louveciennes</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>45 Rue du Général Leclerc, 78430 Louveciennes</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>08 00 07 84 30</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>mailto:plateformeaidants-78sjl@monsieurvincent.asso.fr</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Soutien pour accompagner à domicile un proche atteint de la maladie d'Alzheimer ; temps de répit à domicile (48h/an, Forfait Temps-Libre).</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>48.8672</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>2.1246</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>gryn-groupes-soutien-78</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Groupes de soutien aux aidants — Réseau GRYN</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sartrouville</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>EHPAD Stéphanie, 1 Rue Bordin, 78500 Sartrouville (également au Club Louis XV, Place André-Malraux, 78100 Saint-Germain-en-Laye)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>01 30 61 70 16</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>http://gryn.fr/</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Réunions mensuelles gratuites, animées par une psychologue, pour les aidants d'un proche âgé atteint de la maladie d'Alzheimer ou apparentée : échanges d'expérience, outils concrets pour le quotidien. Le 2e mardi du mois à l'EHPAD Stéphanie (Sartrouville), le 4e jeudi du mois au Club Louis XV (Saint-Germain-en-Laye).</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>48.9385</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2.1608</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ayda-78</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Action Yvelinoise au Développement de l'Aide aux Aidants (AYDA)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Meulan-en-Yvelines</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>25 Avenue des Aulnes, 78250 Meulan-en-Yvelines</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>01 34 74 80 60</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Soutien, information et accompagnement pour les aidants familiaux.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>49.0089</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1.9089</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>bistrot-memoire-houilles-78</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Bistrot Mémoire Houilles</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Houilles</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3 Place du 14 Juillet, 78800 Houilles</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>06 52 13 61 31</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Lieu d'accueil hebdomadaire dans un café, pour les personnes vivant avec des troubles de la mémoire et leurs proches aidants : échanges, activités, accompagnement par des bénévoles formés à l'écoute.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>48.9276</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2.1877</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>halte-repit-alzheimer-carrieres-78</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Halte-Répit-Détente-Alzheimer (HRDA) Carrières-sur-Seine</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Carrières-sur-Seine</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>78 — Yvelines</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>01 39 52 67 77</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Halte-répit ouverte le mardi après-midi pour les aidants d'un proche âgé en perte d'autonomie atteint de la maladie d'Alzheimer.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>48.9053</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2.1685</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>france-alzheimer-91</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>France Alzheimer Essonne</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Corbeil-Essonnes</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>91 — Essonne</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>52 Rue Louis Robert, 91100 Corbeil-Essonnes</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>01 60 88 20 07</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Écoute, groupes de parole (dont en visioconférence, un mercredi par mois), cafés mémoire, formation des aidants, ateliers de gestion du stress et des émotions.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>48.6111</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2.4808</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>pfr-arpajon-91</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Centre Hospitalier d'Arpajon</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Arpajon</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>91 — Essonne</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>18 Avenue de Verdun, 91290 Arpajon</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>01 64 92 95 02</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour la personne malade et temps de répit pour l'aidant.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>48.5895</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2.2517</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>pfr-ballainvilliers-91</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Hôpital gériatrique Les Magnolias</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ballainvilliers</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>91 — Essonne</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>77 Rue du Perray, 91160 Ballainvilliers</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>01 69 80 46 64</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour la personne malade et temps de répit pour l'aidant.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>48.6449</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>2.2928</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>pfr-nid-aidants-91</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Le Nid des Aidants 91</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Yerres</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>91 — Essonne</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>70 Rue Paul Doumer, 91330 Yerres</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>01 69 83 53 91</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>mailto:essonne@leniddesaidants.fr</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Soutien psychologique individuel, groupes de parole, relayage à domicile, séjours de répit, accueil de jour.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>48.7135</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>2.4886</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fa92-a1-antony</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Antony/Bourg-la-Reine</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bourg-la-Reine</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Espace Françoise Dolto, Porte 3, 116 Avenue du Général Leclerc, 92340 Bourg-la-Reine</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01 46 63 11 38</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mailto:fa92.sud@orange.fr</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Permanence le 3e lundi du mois de 10h à 12h. Contacts : Jeanne Cave (permanence) 01 46 63 11 38, Irène Moulin 06 45 86 49 77. Villes couvertes : Antony, Bourg-la-Reine.</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>48.7789</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.3092</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fa92-a2-clamart</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Clamart (Sud 1)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Clamart</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Maison des Associations, 13 bis rue de Bièvres, 92140 Clamart</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01 46 42 22 16</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>mailto:fa92.sud1@yahoo.com</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Permanence le 2e lundi du mois de 13h30 à 15h30. Egalement permanence sur rendez-vous à l'Espace séniors, 5 rue Marcelin Berthelot, 92130 Issy-les-Moulineaux. Villes couvertes : Bagneux, Châtillon, Clamart, Issy-les-Moulineaux, Malakoff, Meudon, Montrouge, Sèvres, Vanves.</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>48.8014</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.2673</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fa92-a3-fontenay</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Fontenay-aux-Roses</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fontenay-aux-Roses</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>06 17 34 47 13</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mailto:fa92.sud@orange.fr</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Villes couvertes : Châtenay-Malabry, Fontenay-aux-Roses, Le Plessis-Robinson, Sceaux.</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>48.7889</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.2872</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fa92-a4-rueil</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Rueil-Malmaison</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Rueil-Malmaison</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>06 03 00 18 23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>mailto:fa92nord@gmail.com</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Villes couvertes : Chaville, Garches, Marnes-la-Coquette, Nanterre, Rueil-Malmaison, Saint-Cloud, Suresnes, Vaucresson, Ville-d'Avray.</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>48.8763</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.1802</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fa92-a5-boulogne</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>06 63 00 71 71</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>mailto:jdefranoux@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Contact : Jeanne Defranoux, sur rendez-vous.</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>48.8352</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.241</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fa92-a6-courbevoie</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Courbevoie</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Courbevoie</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>06 03 00 18 23</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mailto:alixdechaumont@hotmail.com</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Villes couvertes : Asnières-sur-Seine, Bois-Colombes, Clichy, Colombes, Courbevoie, Gennevilliers, La Garenne-Colombes, Levallois-Perret, Villeneuve-la-Garenne.</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>48.8979</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.2559</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fa92-a7-neuilly</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FA92 — Antenne Neuilly-sur-Seine (siège départemental)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Neuilly-sur-Seine</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>94 avenue Achille Peretti, 92200 Neuilly-sur-Seine</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01 46 24 68 31</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/hautsdeseine/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Accueil tous les jours en semaine de 13h30 à 17h30 sur rendez-vous. Email : fr92alzheimer@orange.fr. Villes couvertes : Neuilly-sur-Seine, Puteaux.</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>48.8846</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.2686</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>pfr-camelias-92</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Les Camélias</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bois-Colombes</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>30 rue Auguste Bailly, 92270 Bois-Colombes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01 40 86 42 42</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>mailto:aulagnier.fondation@orange.fr</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA.</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>48.9169</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.2698</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>pfr-abondances-92</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — EHPAD Les Abondances</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>49 rue Saint-Denis, 92100 Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01 41 22 57 51</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.lesabondances.fr/para/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : direction@lesabondances.fr</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>48.8352</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.241</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>pfr-lannelongue-92</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Fondation Odilon-Lannelongue</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vanves</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>29 rue Diderot, 92170 Vanves</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>01 46 42 31 51</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.fondation-odilon-lannelongue.fr/plateforme-accompagnement-et-repit-aux-aidants/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : para@fondation-odilon-lannelongue.fr</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>48.8228</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.2892</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pfr-pivoines-delta7-92</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Les Pivoines (Delta 7)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Neuilly-sur-Seine</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>20 rue des Graviers, 92200 Neuilly-sur-Seine</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>07 67 15 71 26</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.delta7.org/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : par92@delta7.org</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>48.8846</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.2686</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cafe-aidants-colombes-92</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Café des Aidants — CLIC Colombes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Colombes</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CLIC, 36 rue du Maréchal Joffre, 92700 Colombes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01 47 60 43 54</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.colombes.fr/les-solidarites/seniors/cafe-des-aidants/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Un vendredi par mois, 15h-16h30, gratuit sur inscription. En partenariat avec la plateforme de répit Les Camélias. Avec le concours financier du Département des Hauts-de-Seine.</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>48.9239</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.2536</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cafe-memoire-issy-92</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Café Mémoire Issy-les-Moulineaux</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>92 — Hauts-de-Seine</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Café Français, Issy-les-Moulineaux</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01 46 42 22 16</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2e mardi du mois, 15h30-17h30. Organisé par l'antenne FA92 Clamart/Sud1.</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>48.8241</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.2734</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fa93-leraincy</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Le Raincy (siège départemental)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Le Raincy</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>91 avenue de la Résistance, 93340 Le Raincy</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>mailto:francealzheimer93@gmail.com</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Accueil mardi, mercredi, jeudi de 14h à 17h, et sur rendez-vous les autres jours.</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>48.8967</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.5117</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fa93-noisylegrand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Noisy-le-Grand</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Noisy-le-Grand</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Maison des associations, 111 piazza du Mont d'Est, 93160 Noisy-le-Grand</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01 45 92 53 85</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3e mercredi du mois, 14h30-16h30. Contact : Philippe Rota, bénévole FA93, 06 50 04 36 34.</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>48.8407</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.5546</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fa93-romainville</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Romainville</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Romainville</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Maison des retraités, 154bis rue de la République, 93230 Romainville</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01 49 45 56 41</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sur rendez-vous.</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>48.8814</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.4444</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fa93-saintdenis</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Saint-Denis (Maison des séniors)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Maison des séniors, 6 rue des Boucheries, 93200 Saint-Denis</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01 49 33 68 34</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sur rendez-vous. Contact : Micheline Lapp, bénévole FA93, 06 17 36 57 90.</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>48.9362</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.3574</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fa93-saintdenis-semard</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Saint-Denis (Maison de quartier Semard)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Maison de quartier Semard, 9/11 rue Émile Chrétien, 93200 Saint-Denis</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sur rendez-vous.</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>48.9362</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.3574</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fa93-bondy</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Bondy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bondy</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Maison Marianne, 47/51 rue Louis Auguste Blanqui, 93140 Bondy</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01 48 50 53 40</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2e mardi du mois, 10h-12h30. Contact : Denise Lauprêtre, bénévole FA93.</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>48.9006</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.4831</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fa93-sevran</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Sevran</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sevran</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Hôpital René Muret, Immeuble Madeleine Brès, 52 avenue du Dr Schaffner, 93270 Sevran</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2e mercredi du mois, 9h30-12h.</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>48.9389</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.5308</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fa93-bobigny</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Bobigny</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Bobigny</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Hôpital Avicenne, Espace Martine Midy, 125 rue de Stalingrad, 93000 Bobigny</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3e mardi du mois, 16h-18h.</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>48.9091</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.4386</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fa93-montreuil</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FA93 — Permanence Montreuil-sous-Bois</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Montreuil</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lieu communiqué lors de la prise de rendez-vous</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2e jeudi du mois, sur rendez-vous.</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>48.8638</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.4432</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pfr-voixdesaidants-93</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — La Voix des Aidants</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Aulnay-sous-Bois</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>7 avenue Coullemont, 93600 Aulnay-sous-Bois</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>06 10 92 36 84</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://coallia.org/etablissement/medico-social-la-voix-des-aidants/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA/Ma Boussole Aidants. Email : pfr.aulnay@coallia.org</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>48.9384</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.4922</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>pfr-emilegerard-93</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Plateforme de Répit Émile Gérard</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Livry-Gargan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>30 allée de Joinville, 93190 Livry-Gargan</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>01 41 70 12 82</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : para@ehpadegerard.com</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>48.9139</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.5361</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>pfr-lerelais-93</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit Le Relais (Les Rives)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Le Pré-Saint-Gervais</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>142 avenue du Belvédère, 93310 Le Pré-Saint-Gervais</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>01 56 27 06 90</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.idf.vyv3.fr/blog/etablissement/plateforme-daccompagnement-et-de-repit-les-rives-le-relais/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : contact.le-relais@idf.vyv3.fr</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>48.8836</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.4048</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>pfr-svp-stains-93</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit des Aidants Saint-Vincent-de-Paul</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Stains</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6 rue du Repos, 93240 Stains</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01 48 27 88 93</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.croix-saint-simon.org/plateforme-accompagnement-repit-aidants-saint-vincent-paul</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Ouverte aux aidants de personnes atteintes de pathologie neuro-évolutive. Source : CNSA. Email : pfr93@lafocss.org</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>48.9564</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.3872</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cafe-memoire-leraincy-93</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Café Mémoire Le Raincy</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Le Raincy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Café Le Fontenoy, 134 avenue de la Résistance, 93340 Le Raincy</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01 41 53 00 05</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4e mardi du mois, 15h-17h. Entrée libre et gratuite.</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>48.8967</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.5117</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cafe-memoire-rosny-93</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Café Mémoire Happy Hour — L'Osteria</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rosny-sous-Bois</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>L'Osteria, café associatif, Rosny-sous-Bois</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Organisé par France Alzheimer 93. Principe : l'aidant arrive et repart quand il veut, avec ou sans la personne malade.</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>48.8703</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.4839</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cafe-memoire-saintouen-93</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Café Mémoire Saint-Ouen</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Saint-Ouen-sur-Seine</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>93 — Seine-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MOB Hotel, 4-6 rue Gambetta, 93400 Saint-Ouen-sur-Seine</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2e mardi du mois, 14h30-16h15. Organisé par France Alzheimer 93.</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>48.9106</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.3346</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fa94-nogent</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>France Alzheimer Val-de-Marne (siège)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Nogent-sur-Marne</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4 rue du Maréchal Vaillant, 94130 Nogent-sur-Marne</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>01 48 72 87 82</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/valdemarne/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Association créée en 1999, première en France à avoir ouvert des lieux d'accueil pour les familles. Email : alzheimer.val-de-marne@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>48.8375</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2.4823</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fa94-halte-perreux</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Halte-relais Le Perreux-sur-Marne</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Le Perreux-sur-Marne</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>06 15 22 59 47</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Organisée par France Alzheimer Val-de-Marne en partenariat avec la municipalité. 3e vendredi du mois, 14h-17h. Groupe de parole pour aidants + atelier art-thérapie pour les malades. Contact : Mme Odile Hourcade. Information datant de 2021-2022, à reconfirmer.</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>48.8385</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2.5023</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>pfr-delta7-villejuif-94</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Delta 7 Val-de-Marne Ouest</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Villejuif</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6 rue du colonel Marchand, 94800 Villejuif</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>06 52 79 18 61</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.delta7.org/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : par94@delta7.org</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>48.7942</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2.3639</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>pfr-rencontre-aidants-94</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — La Rencontre des Aidants</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fontenay-sous-Bois</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>74 avenue de Stalingrad, 94120 Fontenay-sous-Bois</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>06 27 82 58 88</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.gcsms-ehpadpublics94.fr/EHPAD-Fontenay-sous-Bois/3/18/55</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : aidant@mri94.fr</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>48.8497</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2.4771</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>pfr-abbaye-94</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Maison des Aidants de l'Abbaye</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Saint-Maur-des-Fossés</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3 impasse de l'Abbaye, 94100 Saint-Maur-des-Fossés</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01 55 12 17 20</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.valdemarne.fr/a-votre-service/autonomie/maison-des-aidants-de-labbaye</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : residence.abbaye@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>48.7994</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2.4919</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>pfr-pastoureaux-94</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Résidence les Pastoureaux</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Valenton</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>94 — Val-de-Marne</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10 avenue Salvador-Allende, 94460 Valenton</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>01 56 87 21 31</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : lespastoureaux@orpea.net</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2.4667</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fa95-pontoise</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>France Alzheimer Val-d'Oise (siège)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pontoise</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>16 rue Ampère, 95000 Pontoise</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/valdoise/</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Contact via le formulaire du site.</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>49.0511</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2.0975</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fa95-permanence-gonesse</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FA95 — Permanence Centre Hospitalier de Gonesse</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Gonesse</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier Joséphine Baker, Gonesse</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>01 34 53 20 94</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sur rendez-vous, présentiel ou téléphonique. Prise de RDV via le secrétariat de la consultation mémoire.</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>48.9878</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2.4514</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>pfr-novo-pontoise-95</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Hôpital Novo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pontoise</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6 avenue de l'Île de France, Bâtiment F, 95000 Pontoise</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01 30 75 49 96</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://hopital-novo.fr/ch-pontoise/service/plateforme-de-repit/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : plateforme.repit@ght-novo.fr</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>49.0511</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2.0975</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>pfr-entraide-cormeilles-95</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Maison de l'Entraide</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Cormeilles-en-Parisis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>80 rue de Saint-Germain, 95240 Cormeilles-en-Parisis</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>06 69 63 61 19</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://maisonentraide.fr/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Financée par l'ARS. Source : CNSA. Email : contact@maisonentraide.fr</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>48.9836</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.1917</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bistrot-memoire-montmagny-95</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bistrot Mémoire — Résidence Le Patio</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Montmagny</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Résidence Le Patio, 79 rue Jules Ferry, 95360 Montmagny</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01 39 84 45 45</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1er jeudi du mois, 14h30-17h. Animé par la psychologue de l'établissement. Email : residence.lepatio@groupe-mieuxvivre.fr</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>48.9781</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2.3389</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>bistrot-hapi-isle-adam-95</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bistrot HAPI — Association HAPI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>L'Isle-Adam</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Espace Magallon, 5 rue Bergeret, 95290 L'Isle-Adam</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>06 99 15 89 70</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Une fois par mois, 15h-17h. Organisé par l'association HAPI, en lien avec l'accueil de jour de la Fondation Chantepie Mancier. Email : martine.leonhardt@yahoo.fr</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>49.1119</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2.2233</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cafe-aidants-andilly-95</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Salon des Aidants Andilly</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Andilly</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1 rue Aristide Briand, 95580 Andilly</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01 39 83 09 38</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Tous les mardis matin, 10h-12h. Accès libre ; réservation obligatoire si venue avec la personne aidée. Organisé par l'ADMR Est Parisis. Email : admr-estparisis@fede95.admr.org</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>49.0364</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2.3011</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cafe-aidants-beauchamp-95</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Café des Aidants Beauchamp</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Beauchamp</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Résidence autonomie Eugène Robin, 60 avenue Anatole France, 95250 Beauchamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01 34 40 45 79</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Un mardi par mois, 9h-11h, autour d'un thème. Organisé par le CCAS de Beauchamp. Email : ccas@ville-beauchamp.fr</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>49.0264</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2.1875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cafe-aidants-magnyenvexin-95</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Café des Aidants Magny-en-Vexin</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Magny-en-Vexin</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Espace Marianne, 3 boulevard des Cordeliers, 95420 Magny-en-Vexin</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01 34 67 23 83</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Un jeudi par mois, 18h-20h, autour d'un thème. Organisé par Coordinov. Email : g.moulin@magny-en-vexin.fr</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.7833</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cafe-aidants-osny-95</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Café des Aidants Osny</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Osny</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>01 30 32 33 85</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Un vendredi par mois, 17h-19h. Gratuit, en accès libre. Organisé par Coordinov. Email : contact@coordinov.com</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2.0667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cafe-aidants-persan-95</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Café des Aidants Persan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Persan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Maison des séniors Charles Aznavour, 16 rue Ambroise Croizat, 95340 Persan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>01 39 37 48 89</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Un samedi par mois, 10h-12h. Organisé par le CCAS de Persan et la Communauté de Communes du Haut Val d'Oise.</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>49.1444</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2.2722</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cafe-aidants-sarcelles-95</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Café des Aidants Sarcelles</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sarcelles</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Café brasserie restaurant Le Centre, Centre commercial Les Flanades, Place de France, Porte du Marché, 95200 Sarcelles</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01 34 38 20 09</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Un mardi par mois, 17h-18h30. Accès libre et gratuit. Organisé par le CCAS de la ville de Sarcelles (poste 2416).</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>48.9989</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2.3806</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cafe-aidants-villierslebel-95</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Café des Aidants Villiers-le-Bel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Villiers-le-Bel</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>95 — Val-d'Oise</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Foyer Raymond Labry, 95400 Villiers-le-Bel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>01 34 29 29 40</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Un mardi par mois, 14h-16h. Accès libre. Organisé par le CCAS et le réseau national de l'Association Française des Aidants.</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>49.0122</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2.3931</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fa-allier-siege-moulins</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — siège</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Moulins</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Bâtiment "Sésame", 1-3 rue Berthelot, 03000 Moulins</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>04 70 48 51 28</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Permanence les mardis et vendredis de 14h00 à 17h00. Formations gratuites pour aidants familiaux, ateliers détente, entretiens individuels, sophrologie, art-thérapie.</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>46.5665</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3.3327</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-vichy</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Vichy</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Vichy</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Maison des associations, Place de l'Hôtel de Ville, 03200 Vichy</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>07 52 04 59 10</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Permanence le 4e jeudi du mois de 14h00 à 16h00. Groupe de parole et ateliers d'art-thérapie sur place.</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>46.1272</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3.4256</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-montlucon</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Montluçon</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Montluçon</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Fermette des Îlets, Espace Boris Vian, 27 rue des Foucheroux, 03100 Montluçon</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>06 82 37 59 15</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Permanence le 3e lundi du mois de 14h00 à 16h00. Atelier mémoire sur place.</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>46.3403</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2.6039</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-stpourcain</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Saint-Pourçain-sur-Sioule</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Saint-Pourçain-sur-Sioule</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Hôpital, 43 rue des Fossés, 03500 Saint-Pourçain-sur-Sioule</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>04 70 45 32 46</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Permanence le dernier vendredi du mois de 14h00 à 16h00. Groupe de parole sur place.</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>46.3092</v>
+      </c>
+      <c r="K87" t="n">
+        <v>3.2874</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-diou</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Diou</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Diou</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Salle du Prieuré, 03290 Diou</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>09 54 16 75 45</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Permanence les 2e et 4e mercredis du mois de 14h00 à 17h00. Ateliers détente et art-thérapie sur place.</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>46.5011</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3.6499</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-lapalisse</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Lapalisse</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lapalisse</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Maison de services au public, Boulevard de l'Hôtel de Ville, 03120 Lapalisse</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>06 12 47 49 09</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Permanence le 4e vendredi du mois de 14h00 à 16h00.</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>46.2464</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3.6412</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fa-allier-permanence-jaligny</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — permanence de Jaligny-sur-Besbre</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jaligny-sur-Besbre</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Centre social, 1 rue de la Bertranne, 03220 Jaligny-sur-Besbre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>06 74 22 21 83</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Permanence le 2e mercredi du mois de 09h00 à 12h00.</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>46.2372</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3.7132</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fa-allier-halte-relais-itinerante</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>France Alzheimer Allier — Halte-relais itinérante pour aidants et aidés</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lapalisse (à vérifier)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ancienne école — adresse exacte à vérifier (dispositif itinérant, secteur de Lapalisse)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>06 82 37 59 15</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/allier/</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER : accueil tous les 15 jours pour les aidants et leurs aidés ensemble. Lieu exact non confirmé dans nos sources — à valider avant publication.</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>46.2464</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3.6412</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>pfr-allier-moulins</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Centre Hospitalier de Moulins</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Moulins</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10 avenue Général de Gaulle - BP 609, 03000 Moulins</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>04 70 35 77 77</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.ch-moulins-yzeure.fr/annuaires/plateforme-repit-accueil-de-jour/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit pour les aidants, accompagnement individuel.</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>46.5665</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3.3327</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>pfr-allier-yzeure</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Centre Hospitalier d'Yzeure</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Yzeure</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Route de Gennetines - BP 23, 03400 Yzeure</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>04 70 35 77 77</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.ch-moulins-yzeure.fr/annuaires/plateforme-repit-accueil-de-jour/</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit pour les aidants, accompagnement individuel.</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>46.5667</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3.3667</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>pfr-allier-cusset</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — EHPAD de Cusset</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Cusset</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>03 — Allier</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rue Charles Louis Philippe - Côté Cours, 03300 Cusset</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>04 70 98 18 16</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://maisonderetraite-cusset.com/plateforme-de-repit/</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit pour les aidants, accompagnement individuel. Contact : pfar@mrcusset.fr</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>46.1319</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.4514</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fa-puydedome-siege</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>France Alzheimer Puy-de-Dôme — siège</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>7 rue du Pré la Reine, 63000 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>04 73 91 90 22</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/puy-de-dome/</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Permanences, groupes de parole, formations gratuites pour aidants familiaux.</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fa-puydedome-permanence-puyguillaume</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>France Alzheimer Puy-de-Dôme — permanence de Puy-Guillaume</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Puy-Guillaume (à vérifier)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Adresse exacte à vérifier — contact renvoyé vers le siège de Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>04 73 91 90 22</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/puy-de-dome/</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>À VÉRIFIER : aucune adresse distincte confirmée dans nos sources pour cette permanence.</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>45.9611</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3.4519</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>pfr-volcans-chamalieres</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit des Volcans</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chamalières</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Chamalières, 63400</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>04 73 31 76 00</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS. Couvre tout le département du Puy-de-Dôme sauf le secteur des Combrailles.</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>45.7736</v>
+      </c>
+      <c r="K97" t="n">
+        <v>3.0678</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>pfr-combrailles-itinerante</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit itinérante des Combrailles</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Saint-Gervais-d'Auvergne</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1 rue du Général Desaix, 63390 Saint-Gervais-d'Auvergne</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>07 50 65 60 72</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS. Dispositif itinérant sur le secteur des Combrailles. Contact : repit@combrailles.com</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>46.0261</v>
+      </c>
+      <c r="K98" t="n">
+        <v>2.8103</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cafe-aidants-clermontferrand-63</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Café des aidants de Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>07 85 89 05 50</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.aidants.fr/action/cafe-des-aidants-de-clermont-ferrand/</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Organisé par le Relais Amical 63. Temps d'échange mensuel autour d'un thème, animé par un travailleur social et un psychologue. Ouvert à tous les aidants (généraliste, pas spécifique Alzheimer). Contact : chrisandre@gmail.com</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>aj-ambert-63</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Vimal Chabrier</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Ambert</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Rue Anna Rodier, 63600 Ambert</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>04 73 82 71 00</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>direction@ch-ambert.fr</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>45.548</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3.744</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>aj-beauregard-63</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Résidence Gautier</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Beauregard-l'Évêque</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>56 place du Coudert, 63116 Beauregard-l'Évêque</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>04 73 68 02 83</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>direction@ehpadgautier.com</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>45.833</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3.259</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-meleze-63</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Mélèzes</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>120 rue abbé Prevost, 63100 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>04 73 36 88 47</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://clermont-ferrand.fr/le-ccas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>direction@ccas-clermont-ferrand.fr</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>aj-thiers-63</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Le Belvédère</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Thiers</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Route du Fau, 63300 Thiers</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>04 73 51 12 80</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>direction@ch-thiers.fr</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>45.8522</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3.5461</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>aj-pontduchateau-63</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Le Cèdre</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Pont-du-Château</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1 rue du Clos, 63430 Pont-du-Château</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>04 73 83 20 89</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://www.ehpad-le-cedre.com</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>contact@ehpadlecedre.com</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>45.7889</v>
+      </c>
+      <c r="K104" t="n">
+        <v>3.2214</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>aj-brassac-63</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Vallons Fleuris</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Brassac-les-Mines</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Avenue Charles de Gaulle, 63570 Brassac-les-Mines</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>04 73 54 52 52</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>http://ehpad-brassac.com</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>direction@ehpad-brassac.fr</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>45.4014</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3.3186</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>aj-effiat-63</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD d'Effiat</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Effiat</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>45 rue Antoine Coiffier, 63260 Effiat</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>04 73 63 64 12</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>http://maisonderetraite-effiat.com</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>administration@mr-effiat.fr</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>46.0189</v>
+      </c>
+      <c r="K106" t="n">
+        <v>3.3439</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-hortensias-63</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Hortensias</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3 rue Berteaux, 63000 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>04 73 23 67 50</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://clermont-ferrand.fr/le-ccas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>direction@ccas-clermont-ferrand.fr</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-moulin-63</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Le Moulin</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>11 rue Saint-Rames, 63000 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>04 73 14 63 80</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://clermont-ferrand.fr/le-ccas</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>direction@ccas-clermont-ferrand.fr</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-charme-63</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Jardins de la Charme</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>26 rue Jacques Magnier, 63100 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>04 73 74 91 00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://clermont-ferrand.fr/le-ccas</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>direction@ccas-clermont-ferrand.fr</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>aj-chamalieres-63</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Savarounes</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Chamalières</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 rue du Roc Blanc, 63400 Chamalières</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>04 73 31 76 00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://ehpad-les-savarounes.com/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>admission@savarounes.fr</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>45.7736</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.0678</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>aj-aigueperse-63</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Serge Bayle</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Aigueperse</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Rue de l'Hôpital, 63260 Aigueperse</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>04 73 64 40 00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>http://www.mr-aigueperse.com</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>accueil@mr-aigueperse.fr</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>46.0392</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.2103</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>aj-pionsat-63</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD La Louisiane</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Pionsat</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Rue du Collège, 63330 Pionsat</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>04 73 85 60 46</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>accueil@mdrpionsat.fr</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>46.1667</v>
+      </c>
+      <c r="K112" t="n">
+        <v>2.6939</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>aj-maringues-63</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD L'Ombelle</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Maringues</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Rue Beaudet Lafarge, 63350 Maringues</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>04 73 68 60 79</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://maison-retraite-ombelle.com/</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>accueil@ehpad-ombelle.fr</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>45.9111</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3.2589</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>aj-stgermainlembron-63</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Le Verger</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Saint-Germain-Lembron</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Chemin de la Plagne, 63340 Saint-Germain-Lembron</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>04 73 96 42 72</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>http://www.ehpad-leverger.fr/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>secretariat@ehpad-leverger.fr</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>45.4547</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3.2372</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>aj-rochefortmontagne-63</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Sainte-Élisabeth</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Rochefort-Montagne</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>63210 Rochefort-Montagne</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>04 73 65 82 27</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>accueil@ehpad-ste-elisabeth.fr</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>45.6803</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2.8003</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>aj-ceyrat-63</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD de Ceyrat</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ceyrat</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>28 rue Vercingétorix, 63122 Ceyrat</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>04 73 61 54 54</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>mapad@ceyrat.fr</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>45.7397</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3.085</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>aj-issoire-63</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD La Providence</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Issoire</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>9 rue de la Safournière, 63500 Issoire</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>04 73 89 19 81</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>secretariat@la-providence.fr</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>45.5442</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3.2492</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>aj-cunlhat-63</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Mille Sourires</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Cunlhat</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>4 quartier Lamothe, 63590 Cunlhat</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>04 73 72 70 00</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>accueil@ehpadmillesourires.fr</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>45.6094</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3.5308</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>aj-volvic-63</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Au Fil de l'Eau</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Volvic</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>4 rue de Riom, 63530 Volvic</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>04 73 33 43 83</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ehpad.volvic@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>45.8722</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3.0397</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>aj-aulnat-63</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Chènevis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Aulnat</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Rue Léon Maniez, 63510 Aulnat</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>04 73 73 47 30</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>leschenevis@ehpadaulnat.fr</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>45.7864</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3.1633</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>aj-culhat-63</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Groisne Constance</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Culhat</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>63350 Culhat</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>04 73 70 23 55</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://ehpadculhat.fr/</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>accueil@ehpadculhat.fr</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>45.9147</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3.3169</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>aj-cebazat-63</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Les Cinq Sens</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Cébazat</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61 rue de Châteaugay, 63118 Cébazat</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>04 73 75 09 30</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>http://www.chu-clermontferrand.fr</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Direction-HopitalNord@chu-clermontferrand.fr</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>45.8256</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.1231</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>aj-lempdes-63</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lempdes</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Rue Pasteur, 63370 Lempdes</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>04 63 66 08 37</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>ehpad.louispasteur@mairie-lempdes.fr</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>45.7717</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.1806</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>aj-lezoux-63</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Maison Saint-Joseph</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lezoux</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>52 rue des Aises, 63190 Lezoux</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>04 73 68 27 27</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://ehpadsaintjoseph-lezoux.com/</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ehpad@msj-lezoux.com</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>45.8194</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3.3931</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>aj-veyremonton-63</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Le Cap Veyre</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Veyre-Monton</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>34 chemin du Chardonnet, 63960 Veyre-Monton</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>04 63 66 27 38</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.ehpadlecapveyre.ahsm.fr/</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ehpadlecapveyre.contact.cfd@ahsm.fr</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>45.6656</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3.1567</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>aj-perignat-63</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD La Miséricorde</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Pérignat-lès-Sarliève</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>63170 Pérignat-lès-Sarliève</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>04 43 97 72 00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.ahsm.fr/</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>45.7256</v>
+      </c>
+      <c r="K126" t="n">
+        <v>3.1197</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-renouard-63</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Résidence Renouard</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1 rue Renouard, 63000 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>04 73 34 98 00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.emeis.fr/</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>direction.renouard@emeis.com</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K127" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>aj-gerzat-63</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD La Maison du Marronnier Blanc</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Gerzat</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2 rue des Marronniers, 63360 Gerzat</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>08 05 29 17 00</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://adef-residences.com/</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>dir.gerzat@adefresidences.com</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>45.8253</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.1364</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>aj-clermontferrand-neufsoleils-63</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Accueil de jour — EHPAD Résidence Les Neuf Soleils</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>29 rue Marivaux, 63000 Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>04 73 26 34 58</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://omeris.com/</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>les9soleils@omeris.com</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>45.7772</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.087</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>aj-steeloylesmines-63</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Accueil de jour — Le Jardin d'Aloïs</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Saint-Éloy-les-Mines</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>63 — Puy-de-Dôme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Allée du Jardin d'Alois, 63700 Saint-Éloy-les-Mines</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>04 73 52 37 82</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.sainteloylesmines.fr/centre-communal-daction-sociale/les-structures/le-jardin-d-alois/</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ccas.jardindalois@sainteloylesmines.fr</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>46.1667</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2.8442</v>
       </c>
     </row>
   </sheetData>

--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1129">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2676,6 +2676,672 @@
   </si>
   <si>
     <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Alquier-Debrousse (Ville de Paris). Email : casvp-ehpad-alquierdebrousse@paris.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-murat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier de Murat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accueil-jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 — Cantal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Rue Porte Saint-Esprit, 15300 Murat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 20 30 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD du Centre hospitalier de Murat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-saint-flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier de Saint-Flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Combe de Volzac (D721), 15100 Saint-Flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 60 64 64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier de Saint-Flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-condat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier de Condat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Route de Bort, 15190 Condat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 78 40 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'hôpital local de Condat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD du Pays vert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Rue Fernand Talandier, 15200 Mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 67 33 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier de Mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-laroquebrou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Le Floret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laroquebrou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue Emile Dumas, 15150 Laroquebrou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 46 02 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Le Floret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-montsalvy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Le Château</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montsalvy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du Tour de Ville, 15120 Montsalvy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 49 24 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à la Maison d'Accueil pour Personnes Âgées de Montsalvy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-maurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Roger Jalenques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Rue Antonin Fel, 15600 Maurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 49 01 92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Roger Jalenques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-aurillac-taurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Louis Taurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Rue de la Jordanne, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 64 28 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Louis Taurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-aurillac-mondor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier Henri Mondor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 Av. de la République, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 46 56 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier Henri Mondor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-aurillac-capblanc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Maisonnée Le Cap Blanc (Groupe Emera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Montée de Limagne, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 45 28 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.emera.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Maisonnée Le Cap Blanc, unité dédiée Alzheimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-aurillac-coquelicots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Les Coquelicots (Le Clos des Alouettes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Rue Marie Landes, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 64 16 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour autonome dédié Alzheimer, non rattaché à un EHPAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-lepuy-belhorizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Bel Horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 — Haute-Loire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue de Dunkerque, 43000 Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 09 89 89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Bel Horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-retournac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD de Retournac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retournac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Chemin des Rochettes, 43130 Retournac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 59 42 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD de Retournac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-beaulieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Foyer Notre-Dame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beaulieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169 Route du Pont de Margeaix, 43800 Beaulieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 08 50 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Notre-Dame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-lepuy-vergerdelea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Le Verger de Léa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190 Chem. de Bonnassieu, 43000 Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 02 16 99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Le Verger de Léa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-craponne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier de Craponne-sur-Arzon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Craponne-sur-Arzon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Rue de la Ratille, 43500 Craponne-sur-Arzon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 01 10 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier de Craponne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-vorey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Marie Goy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du 11 Novembre 1918, 43800 Vorey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 03 42 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Foyer de Personnes Âgées Marie Goy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-langeac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier Pierre Gallice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langeac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du 19 Mars 1962, 43300 Langeac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 74 59 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier Pierre Gallice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-pradelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Saint-Christophe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pradelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue Basse (Les Chalets), 43420 Pradelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 00 80 96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Saint-Christophe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-riotord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Le Pollet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riotord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Pl. de l'Église, 43220 Riotord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 75 12 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à la Maison de Retraite Le Pollet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-saintesigolene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Résidence Sigolène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sainte-Sigolène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du Clos de la Source, 43600 Sainte-Sigolène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 66 61 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à la Maison de Retraite Sigolène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-saugues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Saint-Jacques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saugues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 La Font des Mourgues, 43170 Saugues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 77 74 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD Saint-Jacques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-lepuy-saintjoseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Saint-Joseph (Maison Saint Joseph)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Rue des Farges, 43000 Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 04 36 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à la Maison Saint-Joseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-brioude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Résidence Saint-Dominique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brioude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Bd Dr Devins, 43100 Brioude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 50 82 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché aux Résidences Saint-Dominique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-rosieres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Résidence La Roseraie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosières</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Allée de la Roseraie, 43800 Rosières</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 57 45 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD La Roseraie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-tence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD La Sérigoule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Le Fieu (Route du Fieu), 43190 Tence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 59 81 85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mailto:administration@ehpadlaserigoule.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à l'EHPAD La Sérigoule. Email : administration@ehpadlaserigoule.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-lepuy-mariepia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Marie Pia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 Route de Montredon, 43000 Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 07 55 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre Hospitalier Sainte-Marie (unité Marie Pia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-yssingeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Centre hospitalier d'Yssingeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yssingeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Av. de la Marne, 43200 Yssingeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 65 77 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché au Centre hospitalier d'Yssingeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad-lepuy-nazareth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHPAD Maison Nazareth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 Av. Maréchal Foch, 43000 Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 06 66 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mailto:repit43.nazareth@habitat-humanisme.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil de jour Alzheimer, rattaché à Maison Nazareth (Habitat et Humanisme). Email répit : repit43.nazareth@habitat-humanisme.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">france-alzheimer-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France Alzheimer Cantal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 Av. de la République, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 63 31 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.francealzheimer.org/cantal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association départementale, 3 antennes (Aurillac/Mauriac/Saint-Flour). Groupe de parole, café mémoire, halte-relais, ateliers. Email : contact15@francealzheimer.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">france-alzheimer-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France Alzheimer Haute-Loire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiguilhe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Route de Roderie, Villa Rosalie, 43000 Aiguilhe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 38 21 40 62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.francealzheimer.org/hauteloire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association départementale, permanences Aiguilhe/Yssingeaux, rdv réguliers Brioude/Langeac/Bas-en-Basset. Groupe de parole mensuel, halte-relais, jardin thérapeutique. Email : contact43@francealzheimer.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfr-15-conseildepartemental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme d'accompagnement et de répit — Conseil départemental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plateforme-repit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Av. Gambetta, 15000 Aurillac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 43 14 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispositif de coordination et d'orientation vers accueils de jour/hébergements temporaires, porté par le Conseil départemental du Cantal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfr-15-udaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme d'accompagnement et de répit — UDAF 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mailto:plateforme-repit@udaf15.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispositif de coordination et de répit à domicile porté par l'UDAF 15. Email : plateforme-repit@udaf15.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfr-43-serigoule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme d'accompagnement et de répit — EHPAD La Sérigoule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Le Fieu, 43190 Tence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme de répit rattachée à l'EHPAD La Sérigoule. Email : administration@ehpadlaserigoule.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfr-43-nazareth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme d'accompagnement et de répit — EHPAD Maison Nazareth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 06 64 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme de répit rattachée à Maison Nazareth (Habitat et Humanisme). Email : repit43.nazareth@habitat-humanisme.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccas-champssurtarentaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brin de Causette — via CLIC du Haut Cantal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champs-sur-Tarentaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Bis Pl. de l'Église, 15270 Champs-sur-Tarentaine-Marchal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 78 25 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visites de convivialité à domicile pour aidants/personnes âgées isolées, portées par le CLIC du Haut Cantal (adresse = mairie, point de contact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccas-riomesmontagnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brin de Causette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riom-ès-Montagnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pl. Charles de Gaulle, 15400 Riom-ès-Montagnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 50 65 84 51 / 04 71 78 08 96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visites de convivialité à domicile — contacts Annie Dumont / Marie-Jo Quiers (adresse = mairie, point de contact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ccas-mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brin de Causette — CCAS Mairie de Mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pl. Georges Pompidou, 15200 Mauriac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 71 68 28 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visites de convivialité à domicile portées par le CCAS de Mauriac</t>
   </si>
   <si>
     <t xml:space="preserve">Comment ajouter une ressource</t>
@@ -2751,7 +3417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2776,21 +3442,34 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="13"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2851,16 +3530,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2868,7 +3555,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3124,5016 +3819,6341 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="8.3046875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="35.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="3" t="n">
         <v>48.8712</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>2.3435</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>48.8407</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>2.34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>48.8514</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>2.3405</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>48.8815</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>2.3695</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>48.8395</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>2.3925</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>48.829</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>2.3735</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>48.8391</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>2.2989</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>48.893</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>2.3538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>48.8465</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>2.2838</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>48.8405</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>2.391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>48.8285</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>2.3195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>48.8965</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>2.3605</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="3" t="n">
         <v>48.8566</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>2.3522</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2" t="s">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>48.8566</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>2.3522</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>48.8566</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2.3522</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2" t="s">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="3" t="n">
         <v>48.8407</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>2.34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="3" t="n">
         <v>48.8566</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>2.3522</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="3" t="n">
         <v>48.5769</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>2.6062</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="s">
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="3" t="n">
         <v>48.4453</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>2.7273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2" t="s">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="3" t="n">
         <v>48.402</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>2.7285</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="s">
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="3" t="n">
         <v>48.402</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>2.7285</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2" t="s">
+      <c r="H23" s="3"/>
+      <c r="I23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="3" t="n">
         <v>48.7304</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>2.7725</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="3" t="n">
         <v>48.9532</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>3.1258</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="s">
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="3" t="n">
         <v>48.5389</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="3" t="n">
         <v>48.8049</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>2.1204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="3" t="n">
         <v>48.8672</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>2.1246</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="3" t="n">
         <v>48.9385</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>2.1608</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
+      <c r="H29" s="3"/>
+      <c r="I29" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="3" t="n">
         <v>49.0089</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>1.9089</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2" t="s">
+      <c r="H30" s="3"/>
+      <c r="I30" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="3" t="n">
         <v>48.9276</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>2.1877</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2" t="s">
+      <c r="H31" s="3"/>
+      <c r="I31" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="3" t="n">
         <v>48.9053</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>2.1685</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2" t="s">
+      <c r="H32" s="3"/>
+      <c r="I32" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="3" t="n">
         <v>48.6111</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>2.4808</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
+      <c r="H33" s="3"/>
+      <c r="I33" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="3" t="n">
         <v>48.5895</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>2.2517</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2" t="s">
+      <c r="H34" s="3"/>
+      <c r="I34" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="3" t="n">
         <v>48.6449</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>2.2928</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="3" t="n">
         <v>48.7135</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>2.4886</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="C36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="H36" s="0" t="s">
+      <c r="H36" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="I36" s="0" t="s">
+      <c r="I36" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J36" s="0" t="n">
+      <c r="J36" s="4" t="n">
         <v>48.7789</v>
       </c>
-      <c r="K36" s="0" t="n">
+      <c r="K36" s="4" t="n">
         <v>2.3092</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C37" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="0" t="s">
+      <c r="C37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="H37" s="0" t="s">
+      <c r="H37" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="I37" s="0" t="s">
+      <c r="I37" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="J37" s="0" t="n">
+      <c r="J37" s="4" t="n">
         <v>48.8014</v>
       </c>
-      <c r="K37" s="0" t="n">
+      <c r="K37" s="4" t="n">
         <v>2.2673</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="0" t="s">
+      <c r="C38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="H38" s="0" t="s">
+      <c r="H38" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="I38" s="0" t="s">
+      <c r="I38" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J38" s="0" t="n">
+      <c r="J38" s="4" t="n">
         <v>48.7889</v>
       </c>
-      <c r="K38" s="0" t="n">
+      <c r="K38" s="4" t="n">
         <v>2.2872</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="0" t="s">
+      <c r="C39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="F39" s="4"/>
+      <c r="G39" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H39" s="0" t="s">
+      <c r="H39" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="I39" s="0" t="s">
+      <c r="I39" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J39" s="0" t="n">
+      <c r="J39" s="4" t="n">
         <v>48.8763</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="4" t="n">
         <v>2.1802</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="0" t="s">
+      <c r="C40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="H40" s="0" t="s">
+      <c r="H40" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="I40" s="0" t="s">
+      <c r="I40" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="J40" s="0" t="n">
+      <c r="J40" s="4" t="n">
         <v>48.8352</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="4" t="n">
         <v>2.241</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" s="0" t="s">
+      <c r="C41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H41" s="0" t="s">
+      <c r="H41" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="I41" s="0" t="s">
+      <c r="I41" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J41" s="4" t="n">
         <v>48.8979</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="4" t="n">
         <v>2.2559</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="C42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="H42" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="I42" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="J42" s="0" t="n">
+      <c r="J42" s="4" t="n">
         <v>48.8846</v>
       </c>
-      <c r="K42" s="0" t="n">
+      <c r="K42" s="4" t="n">
         <v>2.2686</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="0" t="s">
+      <c r="C43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H43" s="0" t="s">
+      <c r="H43" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="I43" s="0" t="s">
+      <c r="I43" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="J43" s="0" t="n">
+      <c r="J43" s="4" t="n">
         <v>48.9169</v>
       </c>
-      <c r="K43" s="0" t="n">
+      <c r="K43" s="4" t="n">
         <v>2.2698</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="C44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H44" s="0" t="s">
+      <c r="H44" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I44" s="0" t="s">
+      <c r="I44" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="J44" s="0" t="n">
+      <c r="J44" s="4" t="n">
         <v>48.8352</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="4" t="n">
         <v>2.241</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="0" t="s">
+      <c r="C45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="H45" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="I45" s="0" t="s">
+      <c r="I45" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="J45" s="0" t="n">
+      <c r="J45" s="4" t="n">
         <v>48.8228</v>
       </c>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="4" t="n">
         <v>2.2892</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="0" t="s">
+      <c r="C46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H46" s="0" t="s">
+      <c r="H46" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="I46" s="0" t="s">
+      <c r="I46" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="J46" s="0" t="n">
+      <c r="J46" s="4" t="n">
         <v>48.8846</v>
       </c>
-      <c r="K46" s="0" t="n">
+      <c r="K46" s="4" t="n">
         <v>2.2686</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="H47" s="0" t="s">
+      <c r="H47" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I47" s="0" t="s">
+      <c r="I47" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="J47" s="0" t="n">
+      <c r="J47" s="4" t="n">
         <v>48.9239</v>
       </c>
-      <c r="K47" s="0" t="n">
+      <c r="K47" s="4" t="n">
         <v>2.2536</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="I48" s="0" t="s">
+      <c r="H48" s="4"/>
+      <c r="I48" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="J48" s="0" t="n">
+      <c r="J48" s="4" t="n">
         <v>48.8241</v>
       </c>
-      <c r="K48" s="0" t="n">
+      <c r="K48" s="4" t="n">
         <v>2.2734</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="0" t="s">
+      <c r="C49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H49" s="0" t="s">
+      <c r="H49" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="I49" s="0" t="s">
+      <c r="I49" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="J49" s="0" t="n">
+      <c r="J49" s="4" t="n">
         <v>48.8967</v>
       </c>
-      <c r="K49" s="0" t="n">
+      <c r="K49" s="4" t="n">
         <v>2.5117</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="C50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="G50" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="I50" s="0" t="s">
+      <c r="H50" s="4"/>
+      <c r="I50" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J50" s="4" t="n">
         <v>48.8407</v>
       </c>
-      <c r="K50" s="0" t="n">
+      <c r="K50" s="4" t="n">
         <v>2.5546</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="0" t="s">
+      <c r="C51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="I51" s="0" t="s">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J51" s="4" t="n">
         <v>48.8814</v>
       </c>
-      <c r="K51" s="0" t="n">
+      <c r="K51" s="4" t="n">
         <v>2.4444</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="C52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="I52" s="0" t="s">
+      <c r="H52" s="4"/>
+      <c r="I52" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="J52" s="0" t="n">
+      <c r="J52" s="4" t="n">
         <v>48.9362</v>
       </c>
-      <c r="K52" s="0" t="n">
+      <c r="K52" s="4" t="n">
         <v>2.3574</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C53" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="0" t="s">
+      <c r="C53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="G53" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I53" s="0" t="s">
+      <c r="H53" s="4"/>
+      <c r="I53" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="J53" s="0" t="n">
+      <c r="J53" s="4" t="n">
         <v>48.9362</v>
       </c>
-      <c r="K53" s="0" t="n">
+      <c r="K53" s="4" t="n">
         <v>2.3574</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C54" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" s="0" t="s">
+      <c r="C54" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="G54" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="I54" s="0" t="s">
+      <c r="H54" s="4"/>
+      <c r="I54" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="J54" s="0" t="n">
+      <c r="J54" s="4" t="n">
         <v>48.9006</v>
       </c>
-      <c r="K54" s="0" t="n">
+      <c r="K54" s="4" t="n">
         <v>2.4831</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" s="0" t="s">
+      <c r="C55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="G55" s="0" t="s">
+      <c r="G55" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I55" s="0" t="s">
+      <c r="H55" s="4"/>
+      <c r="I55" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="J55" s="0" t="n">
+      <c r="J55" s="4" t="n">
         <v>48.9389</v>
       </c>
-      <c r="K55" s="0" t="n">
+      <c r="K55" s="4" t="n">
         <v>2.5308</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="0" t="s">
+      <c r="C56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="G56" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I56" s="0" t="s">
+      <c r="H56" s="4"/>
+      <c r="I56" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="J56" s="0" t="n">
+      <c r="J56" s="4" t="n">
         <v>48.9091</v>
       </c>
-      <c r="K56" s="0" t="n">
+      <c r="K56" s="4" t="n">
         <v>2.4386</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" s="0" t="s">
+      <c r="C57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="G57" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I57" s="0" t="s">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="J57" s="0" t="n">
+      <c r="J57" s="4" t="n">
         <v>48.8638</v>
       </c>
-      <c r="K57" s="0" t="n">
+      <c r="K57" s="4" t="n">
         <v>2.4432</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="C58" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" s="0" t="s">
+      <c r="C58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="G58" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="H58" s="0" t="s">
+      <c r="H58" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="I58" s="0" t="s">
+      <c r="I58" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="J58" s="0" t="n">
+      <c r="J58" s="4" t="n">
         <v>48.9384</v>
       </c>
-      <c r="K58" s="0" t="n">
+      <c r="K58" s="4" t="n">
         <v>2.4922</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="0" t="s">
+      <c r="C59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="G59" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="I59" s="0" t="s">
+      <c r="H59" s="4"/>
+      <c r="I59" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="J59" s="0" t="n">
+      <c r="J59" s="4" t="n">
         <v>48.9139</v>
       </c>
-      <c r="K59" s="0" t="n">
+      <c r="K59" s="4" t="n">
         <v>2.5361</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C60" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="0" t="s">
+      <c r="C60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="G60" s="0" t="s">
+      <c r="G60" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H60" s="0" t="s">
+      <c r="H60" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="I60" s="0" t="s">
+      <c r="I60" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="J60" s="0" t="n">
+      <c r="J60" s="4" t="n">
         <v>48.8836</v>
       </c>
-      <c r="K60" s="0" t="n">
+      <c r="K60" s="4" t="n">
         <v>2.4048</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C61" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" s="0" t="s">
+      <c r="C61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="G61" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="H61" s="0" t="s">
+      <c r="H61" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="I61" s="0" t="s">
+      <c r="I61" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="J61" s="0" t="n">
+      <c r="J61" s="4" t="n">
         <v>48.9564</v>
       </c>
-      <c r="K61" s="0" t="n">
+      <c r="K61" s="4" t="n">
         <v>2.3872</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="E62" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="G62" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I62" s="0" t="s">
+      <c r="H62" s="4"/>
+      <c r="I62" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="J62" s="0" t="n">
+      <c r="J62" s="4" t="n">
         <v>48.8967</v>
       </c>
-      <c r="K62" s="0" t="n">
+      <c r="K62" s="4" t="n">
         <v>2.5117</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="E63" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="I63" s="0" t="s">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="J63" s="0" t="n">
+      <c r="J63" s="4" t="n">
         <v>48.8703</v>
       </c>
-      <c r="K63" s="0" t="n">
+      <c r="K63" s="4" t="n">
         <v>2.4839</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E64" s="0" t="s">
+      <c r="E64" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="I64" s="0" t="s">
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="J64" s="0" t="n">
+      <c r="J64" s="4" t="n">
         <v>48.9106</v>
       </c>
-      <c r="K64" s="0" t="n">
+      <c r="K64" s="4" t="n">
         <v>2.3346</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C65" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D65" s="0" t="s">
+      <c r="C65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="E65" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="G65" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="H65" s="0" t="s">
+      <c r="H65" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="I65" s="0" t="s">
+      <c r="I65" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="J65" s="0" t="n">
+      <c r="J65" s="4" t="n">
         <v>48.8375</v>
       </c>
-      <c r="K65" s="0" t="n">
+      <c r="K65" s="4" t="n">
         <v>2.4823</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="F66" s="4"/>
+      <c r="G66" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="I66" s="0" t="s">
+      <c r="H66" s="4"/>
+      <c r="I66" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="J66" s="0" t="n">
+      <c r="J66" s="4" t="n">
         <v>48.8385</v>
       </c>
-      <c r="K66" s="0" t="n">
+      <c r="K66" s="4" t="n">
         <v>2.5023</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C67" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="0" t="s">
+      <c r="C67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="E67" s="0" t="s">
+      <c r="E67" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="G67" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H67" s="0" t="s">
+      <c r="H67" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="I67" s="0" t="s">
+      <c r="I67" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="J67" s="0" t="n">
+      <c r="J67" s="4" t="n">
         <v>48.7942</v>
       </c>
-      <c r="K67" s="0" t="n">
+      <c r="K67" s="4" t="n">
         <v>2.3639</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C68" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" s="0" t="s">
+      <c r="C68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="G68" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="H68" s="0" t="s">
+      <c r="H68" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="I68" s="0" t="s">
+      <c r="I68" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="J68" s="0" t="n">
+      <c r="J68" s="4" t="n">
         <v>48.8497</v>
       </c>
-      <c r="K68" s="0" t="n">
+      <c r="K68" s="4" t="n">
         <v>2.4771</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="C69" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" s="0" t="s">
+      <c r="C69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E69" s="0" t="s">
+      <c r="E69" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="G69" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="H69" s="0" t="s">
+      <c r="H69" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="I69" s="0" t="s">
+      <c r="I69" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="J69" s="0" t="n">
+      <c r="J69" s="4" t="n">
         <v>48.7994</v>
       </c>
-      <c r="K69" s="0" t="n">
+      <c r="K69" s="4" t="n">
         <v>2.4919</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C70" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="0" t="s">
+      <c r="C70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="E70" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="G70" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="I70" s="0" t="s">
+      <c r="H70" s="4"/>
+      <c r="I70" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="J70" s="0" t="n">
+      <c r="J70" s="4" t="n">
         <v>48.75</v>
       </c>
-      <c r="K70" s="0" t="n">
+      <c r="K70" s="4" t="n">
         <v>2.4667</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="C71" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" s="0" t="s">
+      <c r="C71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="E71" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="H71" s="0" t="s">
+      <c r="G71" s="4"/>
+      <c r="H71" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="I71" s="0" t="s">
+      <c r="I71" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="J71" s="0" t="n">
+      <c r="J71" s="4" t="n">
         <v>49.0511</v>
       </c>
-      <c r="K71" s="0" t="n">
+      <c r="K71" s="4" t="n">
         <v>2.0975</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C72" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" s="0" t="s">
+      <c r="C72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="G72" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="I72" s="0" t="s">
+      <c r="H72" s="4"/>
+      <c r="I72" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J72" s="0" t="n">
+      <c r="J72" s="4" t="n">
         <v>48.9878</v>
       </c>
-      <c r="K72" s="0" t="n">
+      <c r="K72" s="4" t="n">
         <v>2.4514</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="C73" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" s="0" t="s">
+      <c r="C73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="E73" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="G73" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="H73" s="0" t="s">
+      <c r="H73" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="I73" s="0" t="s">
+      <c r="I73" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="J73" s="0" t="n">
+      <c r="J73" s="4" t="n">
         <v>49.0511</v>
       </c>
-      <c r="K73" s="0" t="n">
+      <c r="K73" s="4" t="n">
         <v>2.0975</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C74" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" s="0" t="s">
+      <c r="C74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="E74" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="G74" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H74" s="0" t="s">
+      <c r="H74" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="I74" s="0" t="s">
+      <c r="I74" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J74" s="0" t="n">
+      <c r="J74" s="4" t="n">
         <v>48.9836</v>
       </c>
-      <c r="K74" s="0" t="n">
+      <c r="K74" s="4" t="n">
         <v>2.1917</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C75" s="0" t="s">
+      <c r="C75" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="E75" s="0" t="s">
+      <c r="E75" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="G75" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="I75" s="0" t="s">
+      <c r="H75" s="4"/>
+      <c r="I75" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="J75" s="0" t="n">
+      <c r="J75" s="4" t="n">
         <v>48.9781</v>
       </c>
-      <c r="K75" s="0" t="n">
+      <c r="K75" s="4" t="n">
         <v>2.3389</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C76" s="0" t="s">
+      <c r="C76" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="E76" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="G76" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="I76" s="0" t="s">
+      <c r="H76" s="4"/>
+      <c r="I76" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="J76" s="0" t="n">
+      <c r="J76" s="4" t="n">
         <v>49.1119</v>
       </c>
-      <c r="K76" s="0" t="n">
+      <c r="K76" s="4" t="n">
         <v>2.2233</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C77" s="0" t="s">
+      <c r="C77" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="E77" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="G77" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="I77" s="0" t="s">
+      <c r="H77" s="4"/>
+      <c r="I77" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="J77" s="0" t="n">
+      <c r="J77" s="4" t="n">
         <v>49.0364</v>
       </c>
-      <c r="K77" s="0" t="n">
+      <c r="K77" s="4" t="n">
         <v>2.3011</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C78" s="0" t="s">
+      <c r="C78" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="E78" s="0" t="s">
+      <c r="E78" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="G78" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="I78" s="0" t="s">
+      <c r="H78" s="4"/>
+      <c r="I78" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="J78" s="0" t="n">
+      <c r="J78" s="4" t="n">
         <v>49.0264</v>
       </c>
-      <c r="K78" s="0" t="n">
+      <c r="K78" s="4" t="n">
         <v>2.1875</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C79" s="0" t="s">
+      <c r="C79" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="E79" s="0" t="s">
+      <c r="E79" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="G79" s="0" t="s">
+      <c r="G79" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="I79" s="0" t="s">
+      <c r="H79" s="4"/>
+      <c r="I79" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="J79" s="0" t="n">
+      <c r="J79" s="4" t="n">
         <v>49.15</v>
       </c>
-      <c r="K79" s="0" t="n">
+      <c r="K79" s="4" t="n">
         <v>1.7833</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="0" t="s">
+      <c r="C80" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="E80" s="0" t="s">
+      <c r="E80" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="F80" s="4"/>
+      <c r="G80" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="I80" s="0" t="s">
+      <c r="H80" s="4"/>
+      <c r="I80" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="J80" s="0" t="n">
+      <c r="J80" s="4" t="n">
         <v>49.05</v>
       </c>
-      <c r="K80" s="0" t="n">
+      <c r="K80" s="4" t="n">
         <v>2.0667</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="C81" s="0" t="s">
+      <c r="C81" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="E81" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="G81" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="I81" s="0" t="s">
+      <c r="H81" s="4"/>
+      <c r="I81" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="J81" s="0" t="n">
+      <c r="J81" s="4" t="n">
         <v>49.1444</v>
       </c>
-      <c r="K81" s="0" t="n">
+      <c r="K81" s="4" t="n">
         <v>2.2722</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="C82" s="0" t="s">
+      <c r="C82" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="E82" s="0" t="s">
+      <c r="E82" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="G82" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="I82" s="0" t="s">
+      <c r="H82" s="4"/>
+      <c r="I82" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="J82" s="0" t="n">
+      <c r="J82" s="4" t="n">
         <v>48.9989</v>
       </c>
-      <c r="K82" s="0" t="n">
+      <c r="K82" s="4" t="n">
         <v>2.3806</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="C83" s="0" t="s">
+      <c r="C83" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="E83" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="G83" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I83" s="0" t="s">
+      <c r="H83" s="4"/>
+      <c r="I83" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J83" s="0" t="n">
+      <c r="J83" s="4" t="n">
         <v>49.0122</v>
       </c>
-      <c r="K83" s="0" t="n">
+      <c r="K83" s="4" t="n">
         <v>2.3931</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84" s="0" t="s">
+      <c r="C84" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="E84" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="G84" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="H84" s="0" t="s">
+      <c r="H84" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I84" s="0" t="s">
+      <c r="I84" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="J84" s="0" t="n">
+      <c r="J84" s="4" t="n">
         <v>46.5665</v>
       </c>
-      <c r="K84" s="0" t="n">
+      <c r="K84" s="4" t="n">
         <v>3.3327</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="C85" s="0" t="s">
+      <c r="C85" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="E85" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="G85" s="0" t="s">
+      <c r="G85" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="H85" s="0" t="s">
+      <c r="H85" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I85" s="0" t="s">
+      <c r="I85" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="J85" s="0" t="n">
+      <c r="J85" s="4" t="n">
         <v>46.1272</v>
       </c>
-      <c r="K85" s="0" t="n">
+      <c r="K85" s="4" t="n">
         <v>3.4256</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="C86" s="0" t="s">
+      <c r="C86" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="E86" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="G86" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="H86" s="0" t="s">
+      <c r="H86" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I86" s="0" t="s">
+      <c r="I86" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="J86" s="0" t="n">
+      <c r="J86" s="4" t="n">
         <v>46.3403</v>
       </c>
-      <c r="K86" s="0" t="n">
+      <c r="K86" s="4" t="n">
         <v>2.6039</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="C87" s="0" t="s">
+      <c r="C87" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="E87" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="G87" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="H87" s="0" t="s">
+      <c r="H87" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I87" s="0" t="s">
+      <c r="I87" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="J87" s="0" t="n">
+      <c r="J87" s="4" t="n">
         <v>46.3092</v>
       </c>
-      <c r="K87" s="0" t="n">
+      <c r="K87" s="4" t="n">
         <v>3.2874</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C88" s="0" t="s">
+      <c r="C88" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D88" s="0" t="s">
+      <c r="D88" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="E88" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="G88" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="H88" s="0" t="s">
+      <c r="H88" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I88" s="0" t="s">
+      <c r="I88" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="J88" s="0" t="n">
+      <c r="J88" s="4" t="n">
         <v>46.5011</v>
       </c>
-      <c r="K88" s="0" t="n">
+      <c r="K88" s="4" t="n">
         <v>3.6499</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="D89" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="E89" s="0" t="s">
+      <c r="E89" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="G89" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="H89" s="0" t="s">
+      <c r="H89" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I89" s="0" t="s">
+      <c r="I89" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="J89" s="0" t="n">
+      <c r="J89" s="4" t="n">
         <v>46.2464</v>
       </c>
-      <c r="K89" s="0" t="n">
+      <c r="K89" s="4" t="n">
         <v>3.6412</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C90" s="0" t="s">
+      <c r="C90" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D90" s="0" t="s">
+      <c r="D90" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="E90" s="0" t="s">
+      <c r="E90" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="G90" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="H90" s="0" t="s">
+      <c r="H90" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I90" s="0" t="s">
+      <c r="I90" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J90" s="0" t="n">
+      <c r="J90" s="4" t="n">
         <v>46.2372</v>
       </c>
-      <c r="K90" s="0" t="n">
+      <c r="K90" s="4" t="n">
         <v>3.7132</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="C91" s="0" t="s">
+      <c r="C91" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D91" s="0" t="s">
+      <c r="D91" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="E91" s="0" t="s">
+      <c r="E91" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="G91" s="0" t="s">
+      <c r="G91" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="H91" s="0" t="s">
+      <c r="H91" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I91" s="0" t="s">
+      <c r="I91" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="J91" s="0" t="n">
+      <c r="J91" s="4" t="n">
         <v>46.2464</v>
       </c>
-      <c r="K91" s="0" t="n">
+      <c r="K91" s="4" t="n">
         <v>3.6412</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="C92" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D92" s="0" t="s">
+      <c r="C92" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="E92" s="0" t="s">
+      <c r="E92" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="G92" s="0" t="s">
+      <c r="G92" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="H92" s="0" t="s">
+      <c r="H92" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="I92" s="0" t="s">
+      <c r="I92" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="J92" s="0" t="n">
+      <c r="J92" s="4" t="n">
         <v>46.5665</v>
       </c>
-      <c r="K92" s="0" t="n">
+      <c r="K92" s="4" t="n">
         <v>3.3327</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="C93" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" s="0" t="s">
+      <c r="C93" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="E93" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="G93" s="0" t="s">
+      <c r="G93" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="H93" s="0" t="s">
+      <c r="H93" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="I93" s="0" t="s">
+      <c r="I93" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="J93" s="0" t="n">
+      <c r="J93" s="4" t="n">
         <v>46.5667</v>
       </c>
-      <c r="K93" s="0" t="n">
+      <c r="K93" s="4" t="n">
         <v>3.3667</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="C94" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94" s="0" t="s">
+      <c r="C94" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E94" s="0" t="s">
+      <c r="E94" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="G94" s="0" t="s">
+      <c r="G94" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="H94" s="0" t="s">
+      <c r="H94" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="I94" s="0" t="s">
+      <c r="I94" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="J94" s="0" t="n">
+      <c r="J94" s="4" t="n">
         <v>46.1319</v>
       </c>
-      <c r="K94" s="0" t="n">
+      <c r="K94" s="4" t="n">
         <v>3.4514</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" s="0" t="s">
+      <c r="C95" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E95" s="0" t="s">
+      <c r="E95" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="G95" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="H95" s="0" t="s">
+      <c r="H95" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="I95" s="0" t="s">
+      <c r="I95" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="J95" s="0" t="n">
+      <c r="J95" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K95" s="0" t="n">
+      <c r="K95" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="C96" s="0" t="s">
+      <c r="C96" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="D96" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="E96" s="0" t="s">
+      <c r="E96" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="G96" s="0" t="s">
+      <c r="G96" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="H96" s="0" t="s">
+      <c r="H96" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="I96" s="0" t="s">
+      <c r="I96" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="J96" s="0" t="n">
+      <c r="J96" s="4" t="n">
         <v>45.9611</v>
       </c>
-      <c r="K96" s="0" t="n">
+      <c r="K96" s="4" t="n">
         <v>3.4519</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D97" s="0" t="s">
+      <c r="C97" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="E97" s="0" t="s">
+      <c r="E97" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="G97" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I97" s="0" t="s">
+      <c r="H97" s="4"/>
+      <c r="I97" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="J97" s="0" t="n">
+      <c r="J97" s="4" t="n">
         <v>45.7736</v>
       </c>
-      <c r="K97" s="0" t="n">
+      <c r="K97" s="4" t="n">
         <v>3.0678</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D98" s="0" t="s">
+      <c r="C98" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="E98" s="0" t="s">
+      <c r="E98" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="G98" s="0" t="s">
+      <c r="G98" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="I98" s="0" t="s">
+      <c r="H98" s="4"/>
+      <c r="I98" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="J98" s="0" t="n">
+      <c r="J98" s="4" t="n">
         <v>46.0261</v>
       </c>
-      <c r="K98" s="0" t="n">
+      <c r="K98" s="4" t="n">
         <v>2.8103</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C99" s="0" t="s">
+      <c r="C99" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="F99" s="4"/>
+      <c r="G99" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="H99" s="0" t="s">
+      <c r="H99" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="I99" s="0" t="s">
+      <c r="I99" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="J99" s="0" t="n">
+      <c r="J99" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K99" s="0" t="n">
+      <c r="K99" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" s="0" t="s">
+      <c r="C100" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="E100" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="G100" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="I100" s="0" t="s">
+      <c r="H100" s="4"/>
+      <c r="I100" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="J100" s="0" t="n">
+      <c r="J100" s="4" t="n">
         <v>45.548</v>
       </c>
-      <c r="K100" s="0" t="n">
+      <c r="K100" s="4" t="n">
         <v>3.744</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="C101" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D101" s="0" t="s">
+      <c r="C101" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="G101" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="I101" s="0" t="s">
+      <c r="H101" s="4"/>
+      <c r="I101" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="J101" s="0" t="n">
+      <c r="J101" s="4" t="n">
         <v>45.833</v>
       </c>
-      <c r="K101" s="0" t="n">
+      <c r="K101" s="4" t="n">
         <v>3.259</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="C102" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D102" s="0" t="s">
+      <c r="C102" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="G102" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="H102" s="0" t="s">
+      <c r="H102" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="I102" s="0" t="s">
+      <c r="I102" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="J102" s="0" t="n">
+      <c r="J102" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K102" s="0" t="n">
+      <c r="K102" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="C103" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D103" s="0" t="s">
+      <c r="C103" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="G103" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="I103" s="0" t="s">
+      <c r="H103" s="4"/>
+      <c r="I103" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="J103" s="0" t="n">
+      <c r="J103" s="4" t="n">
         <v>45.8522</v>
       </c>
-      <c r="K103" s="0" t="n">
+      <c r="K103" s="4" t="n">
         <v>3.5461</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="C104" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="0" t="s">
+      <c r="C104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="E104" s="0" t="s">
+      <c r="E104" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="G104" s="0" t="s">
+      <c r="G104" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="H104" s="0" t="s">
+      <c r="H104" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="I104" s="0" t="s">
+      <c r="I104" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="J104" s="0" t="n">
+      <c r="J104" s="4" t="n">
         <v>45.7889</v>
       </c>
-      <c r="K104" s="0" t="n">
+      <c r="K104" s="4" t="n">
         <v>3.2214</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C105" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D105" s="0" t="s">
+      <c r="C105" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E105" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="G105" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="H105" s="0" t="s">
+      <c r="H105" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="I105" s="0" t="s">
+      <c r="I105" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="J105" s="0" t="n">
+      <c r="J105" s="4" t="n">
         <v>45.4014</v>
       </c>
-      <c r="K105" s="0" t="n">
+      <c r="K105" s="4" t="n">
         <v>3.3186</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C106" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D106" s="0" t="s">
+      <c r="C106" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="E106" s="0" t="s">
+      <c r="E106" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="G106" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="H106" s="0" t="s">
+      <c r="H106" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="I106" s="0" t="s">
+      <c r="I106" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="J106" s="0" t="n">
+      <c r="J106" s="4" t="n">
         <v>46.0189</v>
       </c>
-      <c r="K106" s="0" t="n">
+      <c r="K106" s="4" t="n">
         <v>3.3439</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D107" s="0" t="s">
+      <c r="C107" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E107" s="0" t="s">
+      <c r="E107" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="G107" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="H107" s="0" t="s">
+      <c r="H107" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="I107" s="0" t="s">
+      <c r="I107" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="J107" s="0" t="n">
+      <c r="J107" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K107" s="0" t="n">
+      <c r="K107" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="C108" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D108" s="0" t="s">
+      <c r="C108" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E108" s="0" t="s">
+      <c r="E108" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="G108" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="H108" s="0" t="s">
+      <c r="H108" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="I108" s="0" t="s">
+      <c r="I108" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="J108" s="0" t="n">
+      <c r="J108" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K108" s="0" t="n">
+      <c r="K108" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C109" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D109" s="0" t="s">
+      <c r="C109" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E109" s="0" t="s">
+      <c r="E109" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="G109" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="H109" s="0" t="s">
+      <c r="H109" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="I109" s="0" t="s">
+      <c r="I109" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="J109" s="0" t="n">
+      <c r="J109" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K109" s="0" t="n">
+      <c r="K109" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="C110" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D110" s="0" t="s">
+      <c r="C110" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="E110" s="0" t="s">
+      <c r="E110" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="G110" s="0" t="s">
+      <c r="G110" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="H110" s="0" t="s">
+      <c r="H110" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="I110" s="0" t="s">
+      <c r="I110" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="J110" s="0" t="n">
+      <c r="J110" s="4" t="n">
         <v>45.7736</v>
       </c>
-      <c r="K110" s="0" t="n">
+      <c r="K110" s="4" t="n">
         <v>3.0678</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D111" s="0" t="s">
+      <c r="C111" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="E111" s="0" t="s">
+      <c r="E111" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="G111" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="H111" s="0" t="s">
+      <c r="H111" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="I111" s="0" t="s">
+      <c r="I111" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="J111" s="0" t="n">
+      <c r="J111" s="4" t="n">
         <v>46.0392</v>
       </c>
-      <c r="K111" s="0" t="n">
+      <c r="K111" s="4" t="n">
         <v>3.2103</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="C112" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D112" s="0" t="s">
+      <c r="C112" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="E112" s="0" t="s">
+      <c r="E112" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="G112" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="I112" s="0" t="s">
+      <c r="H112" s="4"/>
+      <c r="I112" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="J112" s="0" t="n">
+      <c r="J112" s="4" t="n">
         <v>46.1667</v>
       </c>
-      <c r="K112" s="0" t="n">
+      <c r="K112" s="4" t="n">
         <v>2.6939</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="C113" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D113" s="0" t="s">
+      <c r="C113" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="E113" s="0" t="s">
+      <c r="E113" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="G113" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="H113" s="0" t="s">
+      <c r="H113" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="I113" s="0" t="s">
+      <c r="I113" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="J113" s="0" t="n">
+      <c r="J113" s="4" t="n">
         <v>45.9111</v>
       </c>
-      <c r="K113" s="0" t="n">
+      <c r="K113" s="4" t="n">
         <v>3.2589</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="C114" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D114" s="0" t="s">
+      <c r="C114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="E114" s="0" t="s">
+      <c r="E114" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="G114" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="H114" s="0" t="s">
+      <c r="H114" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="I114" s="0" t="s">
+      <c r="I114" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="J114" s="0" t="n">
+      <c r="J114" s="4" t="n">
         <v>45.4547</v>
       </c>
-      <c r="K114" s="0" t="n">
+      <c r="K114" s="4" t="n">
         <v>3.2372</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="C115" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D115" s="0" t="s">
+      <c r="C115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="E115" s="0" t="s">
+      <c r="E115" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="G115" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="I115" s="0" t="s">
+      <c r="H115" s="4"/>
+      <c r="I115" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="J115" s="0" t="n">
+      <c r="J115" s="4" t="n">
         <v>45.6803</v>
       </c>
-      <c r="K115" s="0" t="n">
+      <c r="K115" s="4" t="n">
         <v>2.8003</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" s="0" t="s">
+      <c r="C116" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="E116" s="0" t="s">
+      <c r="E116" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="G116" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="I116" s="0" t="s">
+      <c r="H116" s="4"/>
+      <c r="I116" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J116" s="0" t="n">
+      <c r="J116" s="4" t="n">
         <v>45.7397</v>
       </c>
-      <c r="K116" s="0" t="n">
+      <c r="K116" s="4" t="n">
         <v>3.085</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D117" s="0" t="s">
+      <c r="C117" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="E117" s="0" t="s">
+      <c r="E117" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="F117" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="G117" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="I117" s="0" t="s">
+      <c r="H117" s="4"/>
+      <c r="I117" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="J117" s="0" t="n">
+      <c r="J117" s="4" t="n">
         <v>45.5442</v>
       </c>
-      <c r="K117" s="0" t="n">
+      <c r="K117" s="4" t="n">
         <v>3.2492</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="C118" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D118" s="0" t="s">
+      <c r="C118" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="E118" s="0" t="s">
+      <c r="E118" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="F118" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="G118" s="0" t="s">
+      <c r="G118" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="I118" s="0" t="s">
+      <c r="H118" s="4"/>
+      <c r="I118" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="J118" s="0" t="n">
+      <c r="J118" s="4" t="n">
         <v>45.6094</v>
       </c>
-      <c r="K118" s="0" t="n">
+      <c r="K118" s="4" t="n">
         <v>3.5308</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D119" s="0" t="s">
+      <c r="C119" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="E119" s="0" t="s">
+      <c r="E119" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="G119" s="0" t="s">
+      <c r="G119" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="I119" s="0" t="s">
+      <c r="H119" s="4"/>
+      <c r="I119" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="J119" s="0" t="n">
+      <c r="J119" s="4" t="n">
         <v>45.8722</v>
       </c>
-      <c r="K119" s="0" t="n">
+      <c r="K119" s="4" t="n">
         <v>3.0397</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="C120" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D120" s="0" t="s">
+      <c r="C120" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="E120" s="0" t="s">
+      <c r="E120" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="F120" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="G120" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="I120" s="0" t="s">
+      <c r="H120" s="4"/>
+      <c r="I120" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="J120" s="0" t="n">
+      <c r="J120" s="4" t="n">
         <v>45.7864</v>
       </c>
-      <c r="K120" s="0" t="n">
+      <c r="K120" s="4" t="n">
         <v>3.1633</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D121" s="0" t="s">
+      <c r="C121" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="E121" s="0" t="s">
+      <c r="E121" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="F121" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="G121" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="H121" s="0" t="s">
+      <c r="H121" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="I121" s="0" t="s">
+      <c r="I121" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="J121" s="0" t="n">
+      <c r="J121" s="4" t="n">
         <v>45.9147</v>
       </c>
-      <c r="K121" s="0" t="n">
+      <c r="K121" s="4" t="n">
         <v>3.3169</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="C122" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D122" s="0" t="s">
+      <c r="C122" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="E122" s="0" t="s">
+      <c r="E122" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F122" s="0" t="s">
+      <c r="F122" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="G122" s="0" t="s">
+      <c r="G122" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="H122" s="0" t="s">
+      <c r="H122" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="I122" s="0" t="s">
+      <c r="I122" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="J122" s="0" t="n">
+      <c r="J122" s="4" t="n">
         <v>45.8256</v>
       </c>
-      <c r="K122" s="0" t="n">
+      <c r="K122" s="4" t="n">
         <v>3.1231</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D123" s="0" t="s">
+      <c r="C123" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="E123" s="0" t="s">
+      <c r="E123" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F123" s="0" t="s">
+      <c r="F123" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="G123" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="I123" s="0" t="s">
+      <c r="H123" s="4"/>
+      <c r="I123" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="J123" s="0" t="n">
+      <c r="J123" s="4" t="n">
         <v>45.7717</v>
       </c>
-      <c r="K123" s="0" t="n">
+      <c r="K123" s="4" t="n">
         <v>3.1806</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="C124" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D124" s="0" t="s">
+      <c r="C124" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="E124" s="0" t="s">
+      <c r="E124" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F124" s="0" t="s">
+      <c r="F124" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="G124" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="H124" s="0" t="s">
+      <c r="H124" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="I124" s="0" t="s">
+      <c r="I124" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="J124" s="0" t="n">
+      <c r="J124" s="4" t="n">
         <v>45.8194</v>
       </c>
-      <c r="K124" s="0" t="n">
+      <c r="K124" s="4" t="n">
         <v>3.3931</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="C125" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D125" s="0" t="s">
+      <c r="C125" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="E125" s="0" t="s">
+      <c r="E125" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F125" s="0" t="s">
+      <c r="F125" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="G125" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="H125" s="0" t="s">
+      <c r="H125" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="I125" s="0" t="s">
+      <c r="I125" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="J125" s="0" t="n">
+      <c r="J125" s="4" t="n">
         <v>45.6656</v>
       </c>
-      <c r="K125" s="0" t="n">
+      <c r="K125" s="4" t="n">
         <v>3.1567</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C126" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D126" s="0" t="s">
+      <c r="C126" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="E126" s="0" t="s">
+      <c r="E126" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="F126" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="G126" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="H126" s="0" t="s">
+      <c r="H126" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="J126" s="0" t="n">
+      <c r="I126" s="4"/>
+      <c r="J126" s="4" t="n">
         <v>45.7256</v>
       </c>
-      <c r="K126" s="0" t="n">
+      <c r="K126" s="4" t="n">
         <v>3.1197</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="C127" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D127" s="0" t="s">
+      <c r="C127" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E127" s="0" t="s">
+      <c r="E127" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="F127" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="G127" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="H127" s="0" t="s">
+      <c r="H127" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="I127" s="0" t="s">
+      <c r="I127" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="J127" s="0" t="n">
+      <c r="J127" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K127" s="0" t="n">
+      <c r="K127" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D128" s="0" t="s">
+      <c r="C128" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="E128" s="0" t="s">
+      <c r="E128" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="F128" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="G128" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="H128" s="0" t="s">
+      <c r="H128" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="I128" s="0" t="s">
+      <c r="I128" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="J128" s="0" t="n">
+      <c r="J128" s="4" t="n">
         <v>45.8253</v>
       </c>
-      <c r="K128" s="0" t="n">
+      <c r="K128" s="4" t="n">
         <v>3.1364</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="C129" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D129" s="0" t="s">
+      <c r="C129" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E129" s="0" t="s">
+      <c r="E129" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F129" s="0" t="s">
+      <c r="F129" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="G129" s="0" t="s">
+      <c r="G129" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="H129" s="0" t="s">
+      <c r="H129" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="I129" s="0" t="s">
+      <c r="I129" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="J129" s="0" t="n">
+      <c r="J129" s="4" t="n">
         <v>45.7772</v>
       </c>
-      <c r="K129" s="0" t="n">
+      <c r="K129" s="4" t="n">
         <v>3.087</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="C130" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D130" s="0" t="s">
+      <c r="C130" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="E130" s="0" t="s">
+      <c r="E130" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="F130" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="G130" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="H130" s="0" t="s">
+      <c r="H130" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="I130" s="0" t="s">
+      <c r="I130" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="J130" s="0" t="n">
+      <c r="J130" s="4" t="n">
         <v>46.1667</v>
       </c>
-      <c r="K130" s="0" t="n">
+      <c r="K130" s="4" t="n">
         <v>2.8442</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="C131" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D131" s="0" t="s">
+      <c r="C131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E131" s="0" t="s">
+      <c r="E131" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F131" s="0" t="s">
+      <c r="F131" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="G131" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="H131" s="0" t="s">
+      <c r="H131" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="I131" s="0" t="s">
+      <c r="I131" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="J131" s="0" t="n">
+      <c r="J131" s="4" t="n">
         <v>48.8615</v>
       </c>
-      <c r="K131" s="0" t="n">
+      <c r="K131" s="4" t="n">
         <v>2.3645</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="C132" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D132" s="0" t="s">
+      <c r="C132" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E132" s="0" t="s">
+      <c r="E132" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F132" s="0" t="s">
+      <c r="F132" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="G132" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="H132" s="0" t="s">
+      <c r="H132" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="I132" s="0" t="s">
+      <c r="I132" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="J132" s="0" t="n">
+      <c r="J132" s="4" t="n">
         <v>48.858</v>
       </c>
-      <c r="K132" s="0" t="n">
+      <c r="K132" s="4" t="n">
         <v>2.362</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="C133" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D133" s="0" t="s">
+      <c r="C133" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E133" s="0" t="s">
+      <c r="E133" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="F133" s="4" t="s">
         <v>795</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="G133" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="I133" s="0" t="s">
+      <c r="H133" s="4"/>
+      <c r="I133" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="J133" s="0" t="n">
+      <c r="J133" s="4" t="n">
         <v>48.8534</v>
       </c>
-      <c r="K133" s="0" t="n">
+      <c r="K133" s="4" t="n">
         <v>2.3316</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="C134" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134" s="0" t="s">
+      <c r="C134" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E134" s="0" t="s">
+      <c r="E134" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="F134" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="G134" s="4" t="s">
         <v>801</v>
       </c>
-      <c r="H134" s="0" t="s">
+      <c r="H134" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="I134" s="0" t="s">
+      <c r="I134" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="J134" s="0" t="n">
+      <c r="J134" s="4" t="n">
         <v>48.8778</v>
       </c>
-      <c r="K134" s="0" t="n">
+      <c r="K134" s="4" t="n">
         <v>2.3352</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="4" t="s">
         <v>804</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="4" t="s">
         <v>805</v>
       </c>
-      <c r="C135" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D135" s="0" t="s">
+      <c r="C135" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E135" s="0" t="s">
+      <c r="E135" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F135" s="0" t="s">
+      <c r="F135" s="4" t="s">
         <v>806</v>
       </c>
-      <c r="G135" s="0" t="s">
+      <c r="G135" s="4" t="s">
         <v>807</v>
       </c>
-      <c r="H135" s="0" t="s">
+      <c r="H135" s="4" t="s">
         <v>808</v>
       </c>
-      <c r="I135" s="0" t="s">
+      <c r="I135" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="J135" s="0" t="n">
+      <c r="J135" s="4" t="n">
         <v>48.86</v>
       </c>
-      <c r="K135" s="0" t="n">
+      <c r="K135" s="4" t="n">
         <v>2.3745</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C136" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D136" s="0" t="s">
+      <c r="C136" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E136" s="0" t="s">
+      <c r="E136" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F136" s="0" t="s">
+      <c r="F136" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="G136" s="0" t="s">
+      <c r="G136" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="H136" s="0" t="s">
+      <c r="H136" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="I136" s="0" t="s">
+      <c r="I136" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="J136" s="0" t="n">
+      <c r="J136" s="4" t="n">
         <v>48.8405</v>
       </c>
-      <c r="K136" s="0" t="n">
+      <c r="K136" s="4" t="n">
         <v>2.391</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="C137" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D137" s="0" t="s">
+      <c r="C137" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E137" s="0" t="s">
+      <c r="E137" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F137" s="0" t="s">
+      <c r="F137" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="G137" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="H137" s="0" t="s">
+      <c r="H137" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="I137" s="0" t="s">
+      <c r="I137" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="J137" s="0" t="n">
+      <c r="J137" s="4" t="n">
         <v>48.8225</v>
       </c>
-      <c r="K137" s="0" t="n">
+      <c r="K137" s="4" t="n">
         <v>2.3665</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="C138" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D138" s="0" t="s">
+      <c r="C138" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="0" t="s">
+      <c r="E138" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F138" s="0" t="s">
+      <c r="F138" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="G138" s="0" t="s">
+      <c r="G138" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="I138" s="0" t="s">
+      <c r="H138" s="4"/>
+      <c r="I138" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="J138" s="0" t="n">
+      <c r="J138" s="4" t="n">
         <v>48.833</v>
       </c>
-      <c r="K138" s="0" t="n">
+      <c r="K138" s="4" t="n">
         <v>2.343</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D139" s="0" t="s">
+      <c r="C139" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E139" s="0" t="s">
+      <c r="E139" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F139" s="0" t="s">
+      <c r="F139" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="G139" s="0" t="s">
+      <c r="G139" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="H139" s="0" t="s">
+      <c r="H139" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="I139" s="0" t="s">
+      <c r="I139" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="J139" s="0" t="n">
+      <c r="J139" s="4" t="n">
         <v>48.828</v>
       </c>
-      <c r="K139" s="0" t="n">
+      <c r="K139" s="4" t="n">
         <v>2.373</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="C140" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="0" t="s">
+      <c r="C140" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E140" s="0" t="s">
+      <c r="E140" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F140" s="0" t="s">
+      <c r="F140" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="G140" s="0" t="s">
+      <c r="G140" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="H140" s="0" t="s">
+      <c r="H140" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="I140" s="0" t="s">
+      <c r="I140" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="J140" s="0" t="n">
+      <c r="J140" s="4" t="n">
         <v>48.8285</v>
       </c>
-      <c r="K140" s="0" t="n">
+      <c r="K140" s="4" t="n">
         <v>2.3195</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+      <c r="A141" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="C141" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D141" s="0" t="s">
+      <c r="C141" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E141" s="0" t="s">
+      <c r="E141" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F141" s="0" t="s">
+      <c r="F141" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="G141" s="0" t="s">
+      <c r="G141" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="I141" s="0" t="s">
+      <c r="H141" s="4"/>
+      <c r="I141" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="J141" s="0" t="n">
+      <c r="J141" s="4" t="n">
         <v>48.846</v>
       </c>
-      <c r="K141" s="0" t="n">
+      <c r="K141" s="4" t="n">
         <v>2.2845</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+      <c r="A142" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="C142" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D142" s="0" t="s">
+      <c r="C142" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E142" s="0" t="s">
+      <c r="E142" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F142" s="0" t="s">
+      <c r="F142" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="G142" s="0" t="s">
+      <c r="G142" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="H142" s="0" t="s">
+      <c r="H142" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="I142" s="0" t="s">
+      <c r="I142" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="J142" s="0" t="n">
+      <c r="J142" s="4" t="n">
         <v>48.8375</v>
       </c>
-      <c r="K142" s="0" t="n">
+      <c r="K142" s="4" t="n">
         <v>2.287</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+      <c r="A143" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="C143" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D143" s="0" t="s">
+      <c r="C143" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E143" s="0" t="s">
+      <c r="E143" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F143" s="0" t="s">
+      <c r="F143" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="G143" s="0" t="s">
+      <c r="G143" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="H143" s="0" t="s">
+      <c r="H143" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="I143" s="0" t="s">
+      <c r="I143" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="J143" s="0" t="n">
+      <c r="J143" s="4" t="n">
         <v>48.842</v>
       </c>
-      <c r="K143" s="0" t="n">
+      <c r="K143" s="4" t="n">
         <v>2.3145</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+      <c r="A144" s="4" t="s">
         <v>853</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="C144" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D144" s="0" t="s">
+      <c r="C144" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E144" s="0" t="s">
+      <c r="E144" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F144" s="0" t="s">
+      <c r="F144" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="G144" s="0" t="s">
+      <c r="G144" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="I144" s="0" t="s">
+      <c r="H144" s="4"/>
+      <c r="I144" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="J144" s="0" t="n">
+      <c r="J144" s="4" t="n">
         <v>48.846</v>
       </c>
-      <c r="K144" s="0" t="n">
+      <c r="K144" s="4" t="n">
         <v>2.268</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="s">
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="C145" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D145" s="0" t="s">
+      <c r="C145" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E145" s="0" t="s">
+      <c r="E145" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F145" s="0" t="s">
+      <c r="F145" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="G145" s="0" t="s">
+      <c r="G145" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="H145" s="0" t="s">
+      <c r="H145" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="I145" s="0" t="s">
+      <c r="I145" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="J145" s="0" t="n">
+      <c r="J145" s="4" t="n">
         <v>48.8938</v>
       </c>
-      <c r="K145" s="0" t="n">
+      <c r="K145" s="4" t="n">
         <v>2.3195</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="C146" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D146" s="0" t="s">
+      <c r="C146" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E146" s="0" t="s">
+      <c r="E146" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F146" s="0" t="s">
+      <c r="F146" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="G146" s="0" t="s">
+      <c r="G146" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="H146" s="0" t="s">
+      <c r="H146" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="I146" s="0" t="s">
+      <c r="I146" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="J146" s="0" t="n">
+      <c r="J146" s="4" t="n">
         <v>48.899</v>
       </c>
-      <c r="K146" s="0" t="n">
+      <c r="K146" s="4" t="n">
         <v>2.3595</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="A147" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="C147" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D147" s="0" t="s">
+      <c r="C147" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E147" s="0" t="s">
+      <c r="E147" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F147" s="0" t="s">
+      <c r="F147" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="G147" s="0" t="s">
+      <c r="G147" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="H147" s="0" t="s">
+      <c r="H147" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="I147" s="0" t="s">
+      <c r="I147" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="J147" s="0" t="n">
+      <c r="J147" s="4" t="n">
         <v>48.8825</v>
       </c>
-      <c r="K147" s="0" t="n">
+      <c r="K147" s="4" t="n">
         <v>2.3865</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+      <c r="A148" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="C148" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D148" s="0" t="s">
+      <c r="C148" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E148" s="0" t="s">
+      <c r="E148" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="F148" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="G148" s="0" t="s">
+      <c r="G148" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="H148" s="0" t="s">
+      <c r="H148" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="I148" s="0" t="s">
+      <c r="I148" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="J148" s="0" t="n">
+      <c r="J148" s="4" t="n">
         <v>48.858</v>
       </c>
-      <c r="K148" s="0" t="n">
+      <c r="K148" s="4" t="n">
         <v>2.391</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+      <c r="A149" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="C149" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D149" s="0" t="s">
+      <c r="C149" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E149" s="0" t="s">
+      <c r="E149" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F149" s="0" t="s">
+      <c r="F149" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="G149" s="0" t="s">
+      <c r="G149" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="I149" s="0" t="s">
+      <c r="H149" s="4"/>
+      <c r="I149" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="J149" s="0" t="n">
+      <c r="J149" s="4" t="n">
         <v>48.8635</v>
       </c>
-      <c r="K149" s="0" t="n">
+      <c r="K149" s="4" t="n">
         <v>2.401</v>
       </c>
     </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="J150" s="4" t="n">
+        <v>45.110669</v>
+      </c>
+      <c r="K150" s="4" t="n">
+        <v>2.872562</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="H151" s="4"/>
+      <c r="I151" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>45.029641</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>3.066436</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <v>45.341164</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>2.752773</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>45.216989</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>2.339684</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>44.967234</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>2.193522</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v>44.706356</v>
+      </c>
+      <c r="K155" s="4" t="n">
+        <v>2.500802</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="H156" s="4"/>
+      <c r="I156" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>44.713561</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <v>2.199294</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="H157" s="4"/>
+      <c r="I157" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v>44.918899</v>
+      </c>
+      <c r="K157" s="4" t="n">
+        <v>2.441877</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="H158" s="4"/>
+      <c r="I158" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>44.926327</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>2.435921</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v>44.939207</v>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>2.454544</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>44.927762</v>
+      </c>
+      <c r="K160" s="4" t="n">
+        <v>2.431307</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="J161" s="4" t="n">
+        <v>45.038858</v>
+      </c>
+      <c r="K161" s="4" t="n">
+        <v>3.903751</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="H162" s="4"/>
+      <c r="I162" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>45.203188</v>
+      </c>
+      <c r="K162" s="4" t="n">
+        <v>4.031464</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="H163" s="4"/>
+      <c r="I163" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v>45.128225</v>
+      </c>
+      <c r="K163" s="4" t="n">
+        <v>3.938797</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H164" s="4"/>
+      <c r="I164" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="J164" s="4" t="n">
+        <v>45.034171</v>
+      </c>
+      <c r="K164" s="4" t="n">
+        <v>3.891625</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J165" s="4" t="n">
+        <v>45.327972</v>
+      </c>
+      <c r="K165" s="4" t="n">
+        <v>3.840487</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="H166" s="4"/>
+      <c r="I166" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>45.187047</v>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>3.908513</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="H167" s="4"/>
+      <c r="I167" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v>45.095826</v>
+      </c>
+      <c r="K167" s="4" t="n">
+        <v>3.492474</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>44.766455</v>
+      </c>
+      <c r="K168" s="4" t="n">
+        <v>3.883051</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H169" s="4"/>
+      <c r="I169" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J169" s="4" t="n">
+        <v>45.232882</v>
+      </c>
+      <c r="K169" s="4" t="n">
+        <v>4.401522</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H170" s="4"/>
+      <c r="I170" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J170" s="4" t="n">
+        <v>45.240313</v>
+      </c>
+      <c r="K170" s="4" t="n">
+        <v>4.231806</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J171" s="4" t="n">
+        <v>44.962429</v>
+      </c>
+      <c r="K171" s="4" t="n">
+        <v>3.545857</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H172" s="4"/>
+      <c r="I172" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>45.046805</v>
+      </c>
+      <c r="K172" s="4" t="n">
+        <v>3.882137</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J173" s="4" t="n">
+        <v>45.291495</v>
+      </c>
+      <c r="K173" s="4" t="n">
+        <v>3.383861</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H174" s="4"/>
+      <c r="I174" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>45.13135</v>
+      </c>
+      <c r="K174" s="4" t="n">
+        <v>3.990171</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J175" s="4" t="n">
+        <v>45.11514</v>
+      </c>
+      <c r="K175" s="4" t="n">
+        <v>4.293366</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H176" s="4"/>
+      <c r="I176" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>45.051473</v>
+      </c>
+      <c r="K176" s="4" t="n">
+        <v>3.901251</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>45.144943</v>
+      </c>
+      <c r="K177" s="4" t="n">
+        <v>4.126439</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>45.037794</v>
+      </c>
+      <c r="K178" s="4" t="n">
+        <v>3.887604</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>44.926012</v>
+      </c>
+      <c r="K179" s="4" t="n">
+        <v>2.440137</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>45.050969</v>
+      </c>
+      <c r="K180" s="4" t="n">
+        <v>3.890086</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H181" s="4"/>
+      <c r="I181" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v>44.926832</v>
+      </c>
+      <c r="K181" s="4" t="n">
+        <v>2.44576</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>44.926012</v>
+      </c>
+      <c r="K182" s="4" t="n">
+        <v>2.440137</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>45.11514</v>
+      </c>
+      <c r="K183" s="4" t="n">
+        <v>4.293366</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>45.037794</v>
+      </c>
+      <c r="K184" s="4" t="n">
+        <v>3.887604</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H185" s="4"/>
+      <c r="I185" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v>45.395567</v>
+      </c>
+      <c r="K185" s="4" t="n">
+        <v>2.561006</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H186" s="4"/>
+      <c r="I186" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>45.281494</v>
+      </c>
+      <c r="K186" s="4" t="n">
+        <v>2.660398</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H187" s="4"/>
+      <c r="I187" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>45.217835</v>
+      </c>
+      <c r="K187" s="4" t="n">
+        <v>2.332402</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I145" r:id="rId1" display="casa17@delta7.asso.fr"/>
+    <hyperlink ref="I145" r:id="rId1" display="Accueil de jour Alzheimer, géré par l'association Delta 7. Email : casa17@delta7.asso.fr"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8153,155 +10173,155 @@
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="8.3046875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>885</v>
+      <c r="A1" s="6" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
+      <c r="A2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>886</v>
+      <c r="A3" s="7" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>887</v>
+      <c r="A4" s="7" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>888</v>
+      <c r="A5" s="7" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>889</v>
+      <c r="A6" s="7" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>890</v>
+      <c r="A7" s="7" t="s">
+        <v>1112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+      <c r="A8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>891</v>
+      <c r="A9" s="6" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>892</v>
+      <c r="B10" s="7" t="s">
+        <v>1114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>893</v>
+      <c r="B11" s="7" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>894</v>
+      <c r="B12" s="7" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>895</v>
+      <c r="B13" s="7" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>896</v>
+      <c r="B14" s="7" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>897</v>
+      <c r="B15" s="7" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>898</v>
+      <c r="B16" s="7" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>899</v>
+      <c r="B17" s="7" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>900</v>
+      <c r="B18" s="7" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>902</v>
+      <c r="A19" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1124</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
+      <c r="A20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>903</v>
+      <c r="A21" s="6" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>904</v>
+      <c r="A22" s="7" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>905</v>
+      <c r="A24" s="6" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>906</v>
+      <c r="A25" s="7" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>

--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.3046875" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.82" customWidth="1" style="9" min="1" max="1"/>
@@ -11428,427 +11428,2647 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="9" t="inlineStr">
         <is>
           <t>ad-renoir-nantes</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="9" t="inlineStr">
         <is>
           <t>EHPAD Renoir — accueil de jour</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" s="9" t="inlineStr">
         <is>
           <t>3 rue Ernest Meissonnier, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G217" s="9" t="inlineStr">
         <is>
           <t>02 55 58 66 24</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H217" s="9" t="inlineStr">
         <is>
           <t>https://metropole.nantes.fr/</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I217" s="9" t="inlineStr">
         <is>
           <t>EHPAD public de la Ville de Nantes, avec un accueil de jour pour les personnes en perte d'autonomie ou atteintes de la maladie d'Alzheimer. Contact : ehpad-renoir@mairie-nantes.fr</t>
         </is>
       </c>
-      <c r="J217" t="n">
+      <c r="J217" s="9" t="n">
         <v>47.2237676</v>
       </c>
-      <c r="K217" t="n">
+      <c r="K217" s="9" t="n">
         <v>-1.5910565</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="9" t="inlineStr">
         <is>
           <t>ad-hirondelle-sevre-nantes</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="9" t="inlineStr">
         <is>
           <t>EHPAD Hirondelle de Sèvre — accueil de jour</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" s="9" t="inlineStr">
         <is>
           <t>112 rue des Bourdonnières, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G218" s="9" t="inlineStr">
         <is>
           <t>02 51 88 79 90</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H218" s="9" t="inlineStr">
         <is>
           <t>https://metropole.nantes.fr/</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I218" s="9" t="inlineStr">
         <is>
           <t>EHPAD public de la Ville de Nantes, avec un accueil de jour pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés. Contact : ehpad-hirondelle@mairie-nantes.fr</t>
         </is>
       </c>
-      <c r="J218" t="n">
+      <c r="J218" s="9" t="n">
         <v>47.1851977</v>
       </c>
-      <c r="K218" t="n">
+      <c r="K218" s="9" t="n">
         <v>-1.5245934</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="9" t="inlineStr">
         <is>
           <t>ad-repos-de-proce-nantes</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="9" t="inlineStr">
         <is>
           <t>EHPAD Le Repos de Procé — accueil de jour</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F219" s="9" t="inlineStr">
         <is>
           <t>29 rue Condorcet, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G219" s="9" t="inlineStr">
         <is>
           <t>02 40 95 29 59</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="9" t="inlineStr">
         <is>
           <t>https://pdl.vyv3.fr/personnes-agees</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" s="9" t="inlineStr">
         <is>
           <t>EHPAD du Groupe VYV (mutualiste), avec un Pôle d'Activités et de Soins Adaptés (PASA) et un accueil de jour pour les personnes atteintes de la maladie d'Alzheimer. Contact : accueil.reposdeproce@vyv3.fr</t>
         </is>
       </c>
-      <c r="J219" t="n">
+      <c r="J219" s="9" t="n">
         <v>47.2207622</v>
       </c>
-      <c r="K219" t="n">
+      <c r="K219" s="9" t="n">
         <v>-1.5850127</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="9" t="inlineStr">
         <is>
           <t>ad-protestante-nantes</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="9" t="inlineStr">
         <is>
           <t>EHPAD Maison de Retraite Protestante — accueil de jour</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F220" s="9" t="inlineStr">
         <is>
           <t>4 rue Louis Marin, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G220" s="9" t="inlineStr">
         <is>
           <t>02 40 69 35 44</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="9" t="inlineStr">
         <is>
           <t>https://www.armeedusalut.fr/etablissements/mrp</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I220" s="9" t="inlineStr">
         <is>
           <t>EHPAD géré par la Fondation de l'Armée du Salut, proposant un accueil de jour pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés. Contact : mrp@armeedusalut.fr</t>
         </is>
       </c>
-      <c r="J220" t="n">
+      <c r="J220" s="9" t="n">
         <v>47.2022912</v>
       </c>
-      <c r="K220" t="n">
+      <c r="K220" s="9" t="n">
         <v>-1.5439111</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="9" t="inlineStr">
         <is>
           <t>ad-parc-de-diane-nantes</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="9" t="inlineStr">
         <is>
           <t>EHPAD Résidence Le Parc de Diane — accueil de jour</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" s="9" t="inlineStr">
         <is>
           <t>16 rue de la Fonderie, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G221" s="9" t="inlineStr">
         <is>
           <t>02 51 79 52 00</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="9" t="inlineStr">
         <is>
           <t>https://leparcdediane.lna-sante.com/</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I221" s="9" t="inlineStr">
         <is>
           <t>Premier EHPAD de la région entièrement dédié à la maladie d'Alzheimer et aux maladies neuro-évolutives apparentées (groupe LNA Santé), avec un accueil de jour de 15 places. Contact : direction.diane@lna-sante.com</t>
         </is>
       </c>
-      <c r="J221" t="n">
+      <c r="J221" s="9" t="n">
         <v>47.2004448</v>
       </c>
-      <c r="K221" t="n">
+      <c r="K221" s="9" t="n">
         <v>-1.5274975</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="9" t="inlineStr">
         <is>
           <t>ad-recollets-nantes</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour des Récollets</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F222" s="9" t="inlineStr">
         <is>
           <t>3 rue des Récollets, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G222" s="9" t="inlineStr">
         <is>
           <t>02 40 89 34 23</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H222" s="9" t="inlineStr">
         <is>
           <t>https://metropole.nantes.fr/seniors-ehpads</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I222" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour public de la Ville de Nantes, structure indépendante (non adossée à un EHPAD), pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés. Contact : recollets-accueil-jour@mairie-nantes.fr</t>
         </is>
       </c>
-      <c r="J222" t="n">
+      <c r="J222" s="9" t="n">
         <v>47.2030087</v>
       </c>
-      <c r="K222" t="n">
+      <c r="K222" s="9" t="n">
         <v>-1.5479108</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="9" t="inlineStr">
         <is>
           <t>ad-haute-mitrie-nantes</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour de la Haute-Mitrie</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
         <is>
           <t>13 rue de la Haute Mitrie, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G223" s="9" t="inlineStr">
         <is>
           <t>02 28 23 63 99</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>https://metropole.nantes.fr/seniors-ehpads</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I223" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour public de la Ville de Nantes, structure indépendante (non adossée à un EHPAD), pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés. Contact : haute-mitrie-accueil-jour@mairie-nantes.fr</t>
         </is>
       </c>
-      <c r="J223" t="n">
+      <c r="J223" s="9" t="n">
         <v>47.2313231</v>
       </c>
-      <c r="K223" t="n">
+      <c r="K223" s="9" t="n">
         <v>-1.5251805</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="9" t="inlineStr">
         <is>
           <t>ad-madeleine-julien-nantes</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour Pavillon Madeleine Julien</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="9" t="inlineStr">
         <is>
           <t>accueil-jour</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D224" s="9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E224" s="9" t="inlineStr">
         <is>
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F224" s="9" t="inlineStr">
         <is>
           <t>2 rue de Courson, 44000 Nantes</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G224" s="9" t="inlineStr">
         <is>
           <t>02 51 86 01 80</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H224" s="9" t="inlineStr">
         <is>
           <t>https://www.maison-retraite-saint-joseph.com/</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I224" s="9" t="inlineStr">
         <is>
           <t>Accueil de jour associatif (association Maison de Retraite Saint Joseph), dédié aux personnes atteintes de troubles cognitifs liés à une maladie neurodégénérative (Alzheimer, Parkinson, troubles vasculaires...), sans condition d'âge. Le bâtiment abrite aussi la Maison des Aidants du CCAS de Nantes.</t>
         </is>
       </c>
-      <c r="J224" t="n">
+      <c r="J224" s="9" t="n">
         <v>47.2240134</v>
       </c>
-      <c r="K224" t="n">
+      <c r="K224" s="9" t="n">
         <v>-1.5436294</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>fa35-siege-saintmalo</t>
+        </is>
+      </c>
+      <c r="B225" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — siège</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Malo</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>8B avenue de Moka, 35400 Saint-Malo</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I225" s="9" t="inlineStr">
+        <is>
+          <t>Siège départemental de France Alzheimer Ille-et-Vilaine, pour toute question ou orientation. Email : contact35@francealzheimer.org.</t>
+        </is>
+      </c>
+      <c r="J225" s="9" t="n">
+        <v>48.6493</v>
+      </c>
+      <c r="K225" s="9" t="n">
+        <v>-2.0257</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>fa35-gp-chantepie</t>
+        </is>
+      </c>
+      <c r="B226" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — groupe de parole (Pôle gériatrique rennais)</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>Chantepie</t>
+        </is>
+      </c>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>Pôle gériatrique rennais, Chantepie</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I226" s="9" t="inlineStr">
+        <is>
+          <t>Groupe de parole gratuit pour les proches aidants, animé par des bénévoles formés. Inscription auprès de France Alzheimer 35 au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J226" s="9" t="n">
+        <v>48.081</v>
+      </c>
+      <c r="K226" s="9" t="n">
+        <v>-1.6142</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>fa35-gp-saintlaurent</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — groupe de parole, Polyclinique Saint-Laurent</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>Polyclinique Saint-Laurent, Rennes</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I227" s="9" t="inlineStr">
+        <is>
+          <t>Groupe de parole gratuit pour les proches aidants. Inscription auprès de France Alzheimer 35 au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J227" s="9" t="n">
+        <v>48.1173</v>
+      </c>
+      <c r="K227" s="9" t="n">
+        <v>-1.6778</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>fa35-gp-aujourlejour-cesson</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — groupe de parole « Au Jour le Jour »</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>Cesson-Sévigné</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Cesson-Sévigné (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I228" s="9" t="inlineStr">
+        <is>
+          <t>Groupe de parole « Au Jour le Jour », gratuit, pour échanger avec d'autres aidants. Inscription auprès de France Alzheimer 35 au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J228" s="9" t="n">
+        <v>48.1225</v>
+      </c>
+      <c r="K228" s="9" t="n">
+        <v>-1.6002</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>fa35-gp-poterie-chartresdebretagne</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — groupe de parole, EHPAD La Poterie</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>Chartres-de-Bretagne</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD La Poterie, Chartres-de-Bretagne</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I229" s="9" t="inlineStr">
+        <is>
+          <t>Groupe de parole gratuit pour les proches aidants. Inscription auprès de France Alzheimer 35 au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J229" s="9" t="n">
+        <v>48.0592</v>
+      </c>
+      <c r="K229" s="9" t="n">
+        <v>-1.7205</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>fa35-groupe-entraide-debutmaladie</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Ille-et-Vilaine — groupe d'entraide en début de maladie</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Rennes (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>Groupe d'entraide pensé pour les personnes malades au tout début de la maladie, afin de parler librement entre elles. Renseignements auprès du secrétariat au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J230" s="9" t="n">
+        <v>48.1173</v>
+      </c>
+      <c r="K230" s="9" t="n">
+        <v>-1.6778</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>assia-una-accompagnement-rennes</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>Assia Réseau UNA — accompagnement Alzheimer, Rennes Métropole</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>27 rue de Gascogne, 35000 Rennes</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>02 99 54 14 87</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>https://www.assia-una.fr</t>
+        </is>
+      </c>
+      <c r="I231" s="9" t="inlineStr">
+        <is>
+          <t>Service d'aide et d'accompagnement à domicile, avec une équipe sensibilisée à la maladie d'Alzheimer, intervenant sur Rennes Métropole.</t>
+        </is>
+      </c>
+      <c r="J231" s="9" t="n">
+        <v>48.1088</v>
+      </c>
+      <c r="K231" s="9" t="n">
+        <v>-1.6488</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>fa35-permanence-clic-rennes</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>Permanence France Alzheimer 35 — CLIC de Rennes</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>CLIC de Rennes</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I232" s="9" t="inlineStr">
+        <is>
+          <t>Permanence d'accueil et d'écoute pour les aidants, tenue par un bénévole de France Alzheimer 35. Prise de rendez-vous au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J232" s="9" t="n">
+        <v>48.1173</v>
+      </c>
+      <c r="K232" s="9" t="n">
+        <v>-1.6778</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>fa35-permanence-maisonusagers-saintlaurent</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>Permanence France Alzheimer 35 — Maison des Usagers, Polyclinique Saint-Laurent</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Maison des Usagers, Polyclinique Saint-Laurent, Rennes</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>02 99 80 86 43</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I233" s="9" t="inlineStr">
+        <is>
+          <t>Permanence d'accueil et d'écoute pour les aidants. Prise de rendez-vous au 02 99 80 86 43.</t>
+        </is>
+      </c>
+      <c r="J233" s="9" t="n">
+        <v>48.1173</v>
+      </c>
+      <c r="K233" s="9" t="n">
+        <v>-1.6778</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>fa35-permanence-mordelles</t>
+        </is>
+      </c>
+      <c r="B234" s="9" t="inlineStr">
+        <is>
+          <t>Permanence France Alzheimer 35 — Plateforme de répit de Mordelles</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>Mordelles</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>Place Toulouse-Lautrec, 35310 Mordelles</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>02 90 02 36 37</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/ille-et-vilaine</t>
+        </is>
+      </c>
+      <c r="I234" s="9" t="inlineStr">
+        <is>
+          <t>Permanence d'accueil et d'écoute pour les aidants, tenue dans les locaux de la plateforme de répit Accompagn'Aidants. Email : accompagnaidants@cias-ouest-rennes.fr.</t>
+        </is>
+      </c>
+      <c r="J234" s="9" t="n">
+        <v>48.0806</v>
+      </c>
+      <c r="K234" s="9" t="n">
+        <v>-1.8339</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>pfr-mordelles-35</t>
+        </is>
+      </c>
+      <c r="B235" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme de répit et d'accompagnement aux aidants de Mordelles</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>plateforme-repit</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>Mordelles</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>Place Toulouse-Lautrec, 35310 Mordelles</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>02 90 02 36 37</t>
+        </is>
+      </c>
+      <c r="I235" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme Accompagn'Aidants (CIAS à l'Ouest de Rennes &amp; Centre Hospitalier Brocéliande) : écoute, information, temps de répit et accompagnement pour les aidants d'un proche fragilisé par l'âge ou une maladie neuro-évolutive. Email : accompagnaidants@cias-ouest-rennes.fr.</t>
+        </is>
+      </c>
+      <c r="J235" s="9" t="n">
+        <v>48.0806</v>
+      </c>
+      <c r="K235" s="9" t="n">
+        <v>-1.8339</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>pfr-rennes-clic</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>Paréo — Plateforme de répit et d'accompagnement des aidants</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>plateforme-repit</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>1 rue du Capitaine Dreyfus, 35136 Saint-Jacques-de-la-Lande</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>02 99 78 01 46</t>
+        </is>
+      </c>
+      <c r="I236" s="9" t="inlineStr">
+        <is>
+          <t>Service public et gratuit d'écoute, d'information et de répit pour les proches aidants de personnes âgées, sur le secteur de Rennes.</t>
+        </is>
+      </c>
+      <c r="J236" s="9" t="n">
+        <v>48.073</v>
+      </c>
+      <c r="K236" s="9" t="n">
+        <v>-1.7196</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>aj-kerelys-simonedebeauvoir-rennes</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>Résidence Simone de Beauvoir — Accueil de jour Kérélys</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>1 place Simone-de-Beauvoir, 35000 Rennes</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés. Contactez l'établissement pour connaître les disponibilités.</t>
+        </is>
+      </c>
+      <c r="J237" s="9" t="n">
+        <v>48.1005</v>
+      </c>
+      <c r="K237" s="9" t="n">
+        <v>-1.647</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>aj-lafresnerie-cessonsevigne</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
+        <is>
+          <t>Centre d'Accueil La Fresnerie</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>Cesson-Sévigné</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>1 rue de la Fresnerie, 35510 Cesson-Sévigné</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés.</t>
+        </is>
+      </c>
+      <c r="J238" s="9" t="n">
+        <v>48.1225</v>
+      </c>
+      <c r="K238" s="9" t="n">
+        <v>-1.6002</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>aj-lucienschroeder-rennes</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Lucien Schroeder — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>28 rue de Redon, 35000 Rennes</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Accueil de jour rattaché à l'EHPAD Lucien Schroeder.</t>
+        </is>
+      </c>
+      <c r="J239" s="9" t="n">
+        <v>48.098</v>
+      </c>
+      <c r="K239" s="9" t="n">
+        <v>-1.706</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>aj-jardinsdhermine-rennes</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>Les Jardins d'Hermine (LNA Santé) — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>55 avenue du Haut-Sancé, 35000 Rennes</t>
+        </is>
+      </c>
+      <c r="I240" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 6 places, géré par le groupe LNA Santé.</t>
+        </is>
+      </c>
+      <c r="J240" s="9" t="n">
+        <v>48.091</v>
+      </c>
+      <c r="K240" s="9" t="n">
+        <v>-1.657</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>aj-budorais-noyalchatillon</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>Résidence de la Budorais (Assia Réseau UNA) — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>Noyal-Châtillon-sur-Seiche</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>5 rue du Moulin, 35230 Noyal-Châtillon-sur-Seiche</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>02 99 05 21 50</t>
+        </is>
+      </c>
+      <c r="I241" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein d'une unité protégée de 25 places. Un hébergement temporaire, y compris de nuit, peut aussi être envisagé selon les disponibilités : n'hésitez pas à vous renseigner directement auprès de l'établissement.</t>
+        </is>
+      </c>
+      <c r="J241" s="9" t="n">
+        <v>48.0644</v>
+      </c>
+      <c r="K241" s="9" t="n">
+        <v>-1.6423</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>aj-rablais-saintjacquesdelalande</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>Résidence de la Rablais — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Jacques-de-la-Lande</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>1 place Salvador-Allende, 35136 Saint-Jacques-de-la-Lande</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Accueil de jour pour personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés.</t>
+        </is>
+      </c>
+      <c r="J242" s="9" t="n">
+        <v>48.073</v>
+      </c>
+      <c r="K242" s="9" t="n">
+        <v>-1.7196</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>aj-troischenes-pace</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Résidence Les Trois Chênes — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>Pacé</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>1 allée André Monnier, 35740 Pacé</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>02 99 60 20 22</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Résidence Les Trois Chênes, doté d'une unité Alzheimer.</t>
+        </is>
+      </c>
+      <c r="J243" s="9" t="n">
+        <v>48.1503</v>
+      </c>
+      <c r="K243" s="9" t="n">
+        <v>-1.7519</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>aj-kerelys-lhermitage</t>
+        </is>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Résidence Kérélys — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>L'Hermitage</t>
+        </is>
+      </c>
+      <c r="E244" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>1 rue de la Grande Lanvière, 35590 L'Hermitage</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>02 99 64 42 20</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Kérélys, doté d'une unité Alzheimer et d'un PASA.</t>
+        </is>
+      </c>
+      <c r="J244" s="9" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="K244" s="9" t="n">
+        <v>-1.8064</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>aj-trehelu-guichen</t>
+        </is>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Le Tréhélu — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>Guichen</t>
+        </is>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>4 rue de Launay, 35580 Guichen</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>02 99 52 07 07</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Le Tréhélu, doté d'une unité Alzheimer.</t>
+        </is>
+      </c>
+      <c r="J245" s="9" t="n">
+        <v>47.9764</v>
+      </c>
+      <c r="K245" s="9" t="n">
+        <v>-1.7789</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>aj-jardinsducastel-chateaugiron</t>
+        </is>
+      </c>
+      <c r="B246" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Les Jardins du Castel — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C246" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>Châteaugiron</t>
+        </is>
+      </c>
+      <c r="E246" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>12 rue Alexis Garnier, 35410 Châteaugiron</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>02 99 37 40 12</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Les Jardins du Castel, établissement labellisé Humanitude.</t>
+        </is>
+      </c>
+      <c r="J246" s="9" t="n">
+        <v>48.053</v>
+      </c>
+      <c r="K246" s="9" t="n">
+        <v>-1.5017</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>aj-kerelys-betton</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Kérélys — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>Betton</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1 rue d'Iroise, 35830 Betton</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>02 99 55 05 50</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Kérélys, doté d'une unité Alzheimer.</t>
+        </is>
+      </c>
+      <c r="J247" s="9" t="n">
+        <v>48.1978</v>
+      </c>
+      <c r="K247" s="9" t="n">
+        <v>-1.6461</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>aj-closdorriere-vernsurseiche</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Résidence Le Clos-d'Orrière — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>Vern-sur-Seiche</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>1 rue Stéphane Hessel, 35770 Vern-sur-Seiche</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>02 99 62 75 48</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 6 places au sein de la Résidence Le Clos d'Orrière, au sud de Rennes.</t>
+        </is>
+      </c>
+      <c r="J248" s="9" t="n">
+        <v>48.0662</v>
+      </c>
+      <c r="K248" s="9" t="n">
+        <v>-1.6103</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>aj-champsbleus-vezinlecoquet</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour « La Rosais » (Résidence Les Champs Bleus)</t>
+        </is>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>Vezin-le-Coquet</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>1 rue de Belle-Ile, 35132 Vezin-le-Coquet</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>02 90 02 37 78</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 10 places pour les personnes présentant des troubles liés à la maladie d'Alzheimer, ouvert aux habitants des communes du CIAS à l'Ouest de Rennes. Email : chb.accueildejour@cias-ouest-rennes.fr.</t>
+        </is>
+      </c>
+      <c r="J249" s="9" t="n">
+        <v>48.1231</v>
+      </c>
+      <c r="K249" s="9" t="n">
+        <v>-1.7509</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>aj-saintalexis-noyalsurvilaine</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
+        <is>
+          <t>Maison de Retraite Privée Conventionnée Saint-Alexis — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>Noyal-sur-Vilaine</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>35 — Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Rue du Patis Simon, 35530 Noyal-sur-Vilaine</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>02 99 00 51 14</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de la Maison de Retraite Privée Conventionnée Saint-Alexis.</t>
+        </is>
+      </c>
+      <c r="J250" s="9" t="n">
+        <v>48.1131</v>
+      </c>
+      <c r="K250" s="9" t="n">
+        <v>-1.5297</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="inlineStr">
+        <is>
+          <t>fa66-siege-perpignan</t>
+        </is>
+      </c>
+      <c r="B251" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Pyrénées-Orientales — siège</t>
+        </is>
+      </c>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F251" s="9" t="inlineStr">
+        <is>
+          <t>13 avenue du Palais des Expositions, 66000 Perpignan</t>
+        </is>
+      </c>
+      <c r="G251" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H251" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Siège de France Alzheimer Pyrénées-Orientales, pour toute question ou orientation.</t>
+        </is>
+      </c>
+      <c r="J251" s="9" t="n">
+        <v>42.7009</v>
+      </c>
+      <c r="K251" s="9" t="n">
+        <v>2.8965</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>fa66-gp-mensuel-perpignan</t>
+        </is>
+      </c>
+      <c r="B252" s="9" t="inlineStr">
+        <is>
+          <t>France Alzheimer Pyrénées-Orientales — groupe de parole mensuel</t>
+        </is>
+      </c>
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F252" s="9" t="inlineStr">
+        <is>
+          <t>13 avenue du Palais des Expositions, 66000 Perpignan</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H252" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I252" s="9" t="inlineStr">
+        <is>
+          <t>Groupe de parole mensuel et gratuit pour les proches aidants. Inscription au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J252" s="9" t="n">
+        <v>42.7009</v>
+      </c>
+      <c r="K252" s="9" t="n">
+        <v>2.8965</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>fa66-cafememoire-perpignan</t>
+        </is>
+      </c>
+      <c r="B253" s="9" t="inlineStr">
+        <is>
+          <t>Café Mémoire et Convivialité — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Perpignan (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G253" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H253" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I253" s="9" t="inlineStr">
+        <is>
+          <t>Rencontre mensuelle, conviviale et gratuite, ouverte aux aidants, aux personnes malades et à toute personne intéressée. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J253" s="9" t="n">
+        <v>42.6887</v>
+      </c>
+      <c r="K253" s="9" t="n">
+        <v>2.8948</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>fa66-matineesdetente</t>
+        </is>
+      </c>
+      <c r="B254" s="9" t="inlineStr">
+        <is>
+          <t>Matinées Détente pour proches aidants — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C254" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Perpignan (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G254" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H254" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Matinées conviviales de détente réservées aux proches aidants. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J254" s="9" t="n">
+        <v>42.6887</v>
+      </c>
+      <c r="K254" s="9" t="n">
+        <v>2.8948</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="inlineStr">
+        <is>
+          <t>fa66-ateliermassage</t>
+        </is>
+      </c>
+      <c r="B255" s="9" t="inlineStr">
+        <is>
+          <t>Atelier massage (bien-être aidants) — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Perpignan (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G255" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H255" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Atelier de massage bien-être réservé aux aidants, pour souffler un moment. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J255" s="9" t="n">
+        <v>42.6887</v>
+      </c>
+      <c r="K255" s="9" t="n">
+        <v>2.8948</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>fa66-atelierpingpong-rivesaltes</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>Atelier Ping Pong couple aidant/aidé — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>Rivesaltes</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Rivesaltes (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Atelier ping-pong partagé entre la personne malade et son aidant, dans un esprit convivial. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J256" s="9" t="n">
+        <v>42.7669</v>
+      </c>
+      <c r="K256" s="9" t="n">
+        <v>2.8664</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="inlineStr">
+        <is>
+          <t>fa66-sortiesculturelles</t>
+        </is>
+      </c>
+      <c r="B257" s="9" t="inlineStr">
+        <is>
+          <t>Sorties culturelles — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Perpignan (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Sorties culturelles proposées régulièrement aux aidants. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J257" s="9" t="n">
+        <v>42.6887</v>
+      </c>
+      <c r="K257" s="9" t="n">
+        <v>2.8948</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>fa66-haltesrelais</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
+        <is>
+          <t>Haltes Relais — France Alzheimer P.O.</t>
+        </is>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Perpignan (lieu précisé lors de l'inscription)</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/pyrenees-orientales</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Temps de « halte relais » permettant à l'aidant de souffler pendant que son proche est accompagné. Renseignements au 04 68 52 22 22.</t>
+        </is>
+      </c>
+      <c r="J258" s="9" t="n">
+        <v>42.6887</v>
+      </c>
+      <c r="K258" s="9" t="n">
+        <v>2.8948</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>pfr66-programme-jeunes-samedis</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="inlineStr">
+        <is>
+          <t>Programme pour personnes malades jeunes (samedis) — La Plateforme des aidants</t>
+        </is>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>plateforme-repit</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>10 rue Vincent-d'Indy, 66000 Perpignan</t>
+        </is>
+      </c>
+      <c r="G259" s="9" t="inlineStr">
+        <is>
+          <t>04 68 28 62 77</t>
+        </is>
+      </c>
+      <c r="I259" s="9" t="inlineStr">
+        <is>
+          <t>Programme du samedi dédié aux personnes malades jeunes et à leurs proches, porté par La Plateforme / Le Grand Platane.</t>
+        </is>
+      </c>
+      <c r="J259" s="9" t="n">
+        <v>42.7009</v>
+      </c>
+      <c r="K259" s="9" t="n">
+        <v>2.8965</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>pfr66-legrandplatane-perpignan</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>La Plateforme — Plateforme de répit et d'accompagnement des aidants familiaux (Le Grand Platane)</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>plateforme-repit</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>10 rue Vincent-d'Indy, 66000 Perpignan</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>04 68 28 62 77</t>
+        </is>
+      </c>
+      <c r="I260" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme de répit et d'accompagnement des aidants familiaux, portée par l'association Le Grand Platane : entretiens individualisés, café mémoire, Temps Libéré (relais à domicile de 1 à 4h), formation des aidants.</t>
+        </is>
+      </c>
+      <c r="J260" s="9" t="n">
+        <v>42.7009</v>
+      </c>
+      <c r="K260" s="9" t="n">
+        <v>2.8965</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>pfr66-prades</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme de répit et d'accompagnement — Hôpital de Prades</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>plateforme-repit</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>Prades</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>Route de Catllar, 66500 Prades</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>04 68 97 78 63</t>
+        </is>
+      </c>
+      <c r="I261" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme de répit et d'accompagnement rattachée à l'hôpital de Prades, couvrant le secteur du Conflent ; accessible aux aidants de tout le département.</t>
+        </is>
+      </c>
+      <c r="J261" s="9" t="n">
+        <v>42.6178</v>
+      </c>
+      <c r="K261" s="9" t="n">
+        <v>2.4222</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>aj-grandplatane-perpignan</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>Le Grand Platane — accueil de jour, Perpignan</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>10 rue Vincent-d'Indy, 66000 Perpignan</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>04 68 28 62 77</t>
+        </is>
+      </c>
+      <c r="I262" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 15 places, au sein du Grand Platane.</t>
+        </is>
+      </c>
+      <c r="J262" s="9" t="n">
+        <v>42.7009</v>
+      </c>
+      <c r="K262" s="9" t="n">
+        <v>2.8965</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>aj-grandplatane-argelessurmer</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>Le Grand Platane — accueil de jour, Argelès-sur-Mer</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>Argelès-sur-Mer</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>17 rue des Perdrix, 66700 Argelès-sur-Mer</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>04 68 52 22 22</t>
+        </is>
+      </c>
+      <c r="I263" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 12 places, antenne du Grand Platane à Argelès-sur-Mer.</t>
+        </is>
+      </c>
+      <c r="J263" s="9" t="n">
+        <v>42.5453</v>
+      </c>
+      <c r="K263" s="9" t="n">
+        <v>3.0219</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>aj-grandplatane-millas</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>Le Grand Platane — accueil de jour, Millas</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>Millas</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>15 rue Hermès, ZA Los Palaus, 66170 Millas</t>
+        </is>
+      </c>
+      <c r="I264" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 12 places, antenne du Grand Platane à Millas.</t>
+        </is>
+      </c>
+      <c r="J264" s="9" t="n">
+        <v>42.7169</v>
+      </c>
+      <c r="K264" s="9" t="n">
+        <v>2.6906</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>aj-ehpad-leboulou</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour EHPAD — Le Boulou</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>Le Boulou</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>19 carrièra Del Puig Sangli, 66160 Le Boulou</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>04 68 51 91 27</t>
+        </is>
+      </c>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour Alzheimer, établissement spécialisé.</t>
+        </is>
+      </c>
+      <c r="J265" s="9" t="n">
+        <v>42.5225</v>
+      </c>
+      <c r="K265" s="9" t="n">
+        <v>2.8333</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>aj-ehpad-bompas</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
+        <is>
+          <t>Centre d'accueil de jour Le Cajou</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>Bompas</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>15 rue Bardou Job, 66430 Bompas</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>04 68 51 91 27</t>
+        </is>
+      </c>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour Alzheimer, établissement spécialisé.</t>
+        </is>
+      </c>
+      <c r="J266" s="9" t="n">
+        <v>42.7423</v>
+      </c>
+      <c r="K266" s="9" t="n">
+        <v>2.9126</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>aj-ehpad-argelessurmer</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Les Capucines — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>Argelès-sur-Mer</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Chemin du Roua, 66700 Argelès-sur-Mer</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>04 68 81 46 51</t>
+        </is>
+      </c>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour distinct de celui du Grand Platane, au sein de l'EHPAD Les Capucines.</t>
+        </is>
+      </c>
+      <c r="J267" s="9" t="n">
+        <v>42.5453</v>
+      </c>
+      <c r="K267" s="9" t="n">
+        <v>3.0219</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>aj-ehpad-saintcyprien</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
+        <is>
+          <t>EHPAD Louis Pasteur — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Cyprien</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>32 rue Edmond Michelet, 66750 Saint-Cyprien</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>04 68 21 37 80</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Accueil de jour au sein de l'EHPAD Louis Pasteur, à 300 mètres de la mer.</t>
+        </is>
+      </c>
+      <c r="J268" s="9" t="n">
+        <v>42.6194</v>
+      </c>
+      <c r="K268" s="9" t="n">
+        <v>3.0339</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>aj-ehpad-pezillalariviere</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>Résidence Mutualiste de Pézilla-la-Rivière — accueil de jour</t>
+        </is>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>accueil-jour</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>Pézilla-la-Rivière</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
+          <t>66 — Pyrénées-Orientales</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>3 rue Força Réal, 66370 Pézilla-la-Rivière</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>04 68 62 60 10</t>
+        </is>
+      </c>
+      <c r="I269" s="9" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 8 places, avec PASA (pôle d'activités et de soins adaptés), au sein de la Résidence Mutualiste.</t>
+        </is>
+      </c>
+      <c r="J269" s="9" t="n">
+        <v>42.6667</v>
+      </c>
+      <c r="K269" s="9" t="n">
+        <v>2.7833</v>
       </c>
     </row>
     <row r="1048576" ht="12.8" customHeight="1" s="10"/>

--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -5663,7 +5663,11 @@
           <t>04 73 82 71 00</t>
         </is>
       </c>
-      <c r="H100" s="12" t="n"/>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ch-ambert.fr/</t>
+        </is>
+      </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
           <t>direction@ch-ambert.fr</t>
@@ -8359,7 +8363,11 @@
           <t>04 71 78 40 00</t>
         </is>
       </c>
-      <c r="H152" s="12" t="n"/>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ch-condat.fr/service/ehpad/</t>
+        </is>
+      </c>
       <c r="I152" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à l'hôpital local de Condat</t>
@@ -8408,7 +8416,11 @@
           <t>04 71 67 33 33</t>
         </is>
       </c>
-      <c r="H153" s="12" t="n"/>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ch-mauriac.fr</t>
+        </is>
+      </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Centre hospitalier de Mauriac</t>
@@ -8555,7 +8567,11 @@
           <t>04 71 49 01 92</t>
         </is>
       </c>
-      <c r="H156" s="12" t="n"/>
+      <c r="H156" s="12" t="inlineStr">
+        <is>
+          <t>https://ehpadrogerjalenques.fr/</t>
+        </is>
+      </c>
       <c r="I156" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à l'EHPAD Roger Jalenques</t>
@@ -8653,7 +8669,11 @@
           <t>04 71 46 56 56</t>
         </is>
       </c>
-      <c r="H158" s="12" t="n"/>
+      <c r="H158" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ch-aurillac.fr</t>
+        </is>
+      </c>
       <c r="I158" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Centre hospitalier Henri Mondor</t>
@@ -9000,7 +9020,11 @@
           <t>04 71 01 10 00</t>
         </is>
       </c>
-      <c r="H165" s="12" t="n"/>
+      <c r="H165" s="12" t="inlineStr">
+        <is>
+          <t>http://www.hopital-craponne.fr</t>
+        </is>
+      </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Centre hospitalier de Craponne</t>
@@ -9049,7 +9073,11 @@
           <t>04 71 03 42 90</t>
         </is>
       </c>
-      <c r="H166" s="12" t="n"/>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>http://www.foyermariegoy.com</t>
+        </is>
+      </c>
       <c r="I166" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Foyer de Personnes Âgées Marie Goy</t>
@@ -9098,7 +9126,11 @@
           <t>04 71 74 59 00</t>
         </is>
       </c>
-      <c r="H167" s="12" t="n"/>
+      <c r="H167" s="12" t="inlineStr">
+        <is>
+          <t>https://hoplangeac.fr</t>
+        </is>
+      </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Centre hospitalier Pierre Gallice</t>
@@ -9147,7 +9179,11 @@
           <t>04 71 00 80 96</t>
         </is>
       </c>
-      <c r="H168" s="12" t="n"/>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>https://ehpad-pradelles.fr/</t>
+        </is>
+      </c>
       <c r="I168" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à l'EHPAD Saint-Christophe</t>
@@ -9245,7 +9281,11 @@
           <t>04 71 66 61 17</t>
         </is>
       </c>
-      <c r="H170" s="12" t="n"/>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>https://residence-sigolene.fr</t>
+        </is>
+      </c>
       <c r="I170" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à la Maison de Retraite Sigolène</t>
@@ -9343,7 +9383,11 @@
           <t>04 71 04 36 34</t>
         </is>
       </c>
-      <c r="H172" s="12" t="n"/>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>https://ehpad-st-joseph.fr</t>
+        </is>
+      </c>
       <c r="I172" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à la Maison Saint-Joseph</t>
@@ -9441,7 +9485,11 @@
           <t>04 71 57 45 33</t>
         </is>
       </c>
-      <c r="H174" s="12" t="n"/>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ahsm.fr/</t>
+        </is>
+      </c>
       <c r="I174" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché à l'EHPAD La Roseraie</t>
@@ -9543,7 +9591,11 @@
           <t>04 71 07 55 55</t>
         </is>
       </c>
-      <c r="H176" s="12" t="n"/>
+      <c r="H176" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ahsm.fr/</t>
+        </is>
+      </c>
       <c r="I176" s="12" t="inlineStr">
         <is>
           <t>Accueil de jour Alzheimer, rattaché au Centre Hospitalier Sainte-Marie (unité Marie Pia)</t>
@@ -15038,7 +15090,11 @@
           <t>5 chemin des Alpins, 38000 Grenoble</t>
         </is>
       </c>
-      <c r="G281" s="11" t="n"/>
+      <c r="G281" s="11" t="inlineStr">
+        <is>
+          <t>04 76 23 11 16</t>
+        </is>
+      </c>
       <c r="H281" s="11" t="n"/>
       <c r="I281" s="11" t="n"/>
       <c r="J281" s="11" t="n">
@@ -15079,7 +15135,11 @@
           <t>1 rue Bévière, 38000 Grenoble</t>
         </is>
       </c>
-      <c r="G282" s="11" t="n"/>
+      <c r="G282" s="11" t="inlineStr">
+        <is>
+          <t>04 76 84 29 60</t>
+        </is>
+      </c>
       <c r="H282" s="11" t="n"/>
       <c r="I282" s="11" t="n"/>
       <c r="J282" s="11" t="n">
@@ -15115,9 +15175,21 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F283" s="11" t="n"/>
-      <c r="G283" s="11" t="n"/>
-      <c r="H283" s="11" t="n"/>
+      <c r="F283" s="11" t="inlineStr">
+        <is>
+          <t>13 rue Joseph Moutin, 38180 Seyssins</t>
+        </is>
+      </c>
+      <c r="G283" s="11" t="inlineStr">
+        <is>
+          <t>04 76 48 40 74</t>
+        </is>
+      </c>
+      <c r="H283" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mutualiteisere.org/</t>
+        </is>
+      </c>
       <c r="I283" s="11" t="inlineStr">
         <is>
           <t>Adresse précise à confirmer auprès de l'établissement.</t>
@@ -15156,9 +15228,21 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F284" s="11" t="n"/>
-      <c r="G284" s="11" t="n"/>
-      <c r="H284" s="11" t="n"/>
+      <c r="F284" s="11" t="inlineStr">
+        <is>
+          <t>4 place Michel de Montaigne, 38320 Eybens</t>
+        </is>
+      </c>
+      <c r="G284" s="11" t="inlineStr">
+        <is>
+          <t>04 76 63 34 30</t>
+        </is>
+      </c>
+      <c r="H284" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mutualiteisere.org/</t>
+        </is>
+      </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
           <t>Adresse précise à confirmer auprès de l'établissement.</t>
@@ -15197,8 +15281,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F285" s="11" t="n"/>
-      <c r="G285" s="11" t="n"/>
+      <c r="F285" s="11" t="inlineStr">
+        <is>
+          <t>15 rue Eugène Charbonnier, 38600 Fontaine</t>
+        </is>
+      </c>
+      <c r="G285" s="11" t="inlineStr">
+        <is>
+          <t>04 38 03 10 50</t>
+        </is>
+      </c>
       <c r="H285" s="11" t="n"/>
       <c r="I285" s="11" t="inlineStr">
         <is>
@@ -15238,8 +15330,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F286" s="11" t="n"/>
-      <c r="G286" s="11" t="n"/>
+      <c r="F286" s="11" t="inlineStr">
+        <is>
+          <t>95 route de Chartreuse, 38700 Corenc</t>
+        </is>
+      </c>
+      <c r="G286" s="11" t="inlineStr">
+        <is>
+          <t>04 76 88 00 36</t>
+        </is>
+      </c>
       <c r="H286" s="11" t="n"/>
       <c r="I286" s="11" t="inlineStr">
         <is>
@@ -15279,8 +15379,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F287" s="11" t="n"/>
-      <c r="G287" s="11" t="n"/>
+      <c r="F287" s="11" t="inlineStr">
+        <is>
+          <t>360 rue de l'Eyrard, 38360 Noyarey</t>
+        </is>
+      </c>
+      <c r="G287" s="11" t="inlineStr">
+        <is>
+          <t>04 76 86 96 60</t>
+        </is>
+      </c>
       <c r="H287" s="11" t="n"/>
       <c r="I287" s="11" t="inlineStr">
         <is>
@@ -15320,8 +15428,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F288" s="11" t="n"/>
-      <c r="G288" s="11" t="n"/>
+      <c r="F288" s="11" t="inlineStr">
+        <is>
+          <t>14 rue Auguste et Edith Goirand, 38800 Le Pont-de-Claix</t>
+        </is>
+      </c>
+      <c r="G288" s="11" t="inlineStr">
+        <is>
+          <t>04 76 29 86 70</t>
+        </is>
+      </c>
       <c r="H288" s="11" t="n"/>
       <c r="I288" s="11" t="inlineStr">
         <is>
@@ -15361,8 +15477,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F289" s="11" t="n"/>
-      <c r="G289" s="11" t="n"/>
+      <c r="F289" s="11" t="inlineStr">
+        <is>
+          <t>6 rue du Gymnase, 38120 Saint-Égrève</t>
+        </is>
+      </c>
+      <c r="G289" s="11" t="inlineStr">
+        <is>
+          <t>04 76 75 44 55</t>
+        </is>
+      </c>
       <c r="H289" s="11" t="n"/>
       <c r="I289" s="11" t="inlineStr">
         <is>
@@ -15402,9 +15526,21 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F290" s="11" t="n"/>
-      <c r="G290" s="11" t="n"/>
-      <c r="H290" s="11" t="n"/>
+      <c r="F290" s="11" t="inlineStr">
+        <is>
+          <t>25 rue des Tillerets, 38450 Saint-Georges-de-Commiers</t>
+        </is>
+      </c>
+      <c r="G290" s="11" t="inlineStr">
+        <is>
+          <t>04 76 13 11 98</t>
+        </is>
+      </c>
+      <c r="H290" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mutualiteisere.org/</t>
+        </is>
+      </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
           <t>Adresse précise à confirmer auprès de l'établissement.</t>
@@ -15443,8 +15579,16 @@
           <t>38 — Isère</t>
         </is>
       </c>
-      <c r="F291" s="11" t="n"/>
-      <c r="G291" s="11" t="n"/>
+      <c r="F291" s="11" t="inlineStr">
+        <is>
+          <t>9 chemin du Mas de Saint Germain, 38700 La Tronche</t>
+        </is>
+      </c>
+      <c r="G291" s="11" t="inlineStr">
+        <is>
+          <t>04 76 41 63 30</t>
+        </is>
+      </c>
       <c r="H291" s="11" t="n"/>
       <c r="I291" s="11" t="inlineStr">
         <is>
@@ -20516,7 +20660,11 @@
           <t>53 chemin de Parenty, 69250 Neuville-sur-Saône</t>
         </is>
       </c>
-      <c r="G395" s="11" t="n"/>
+      <c r="G395" s="11" t="inlineStr">
+        <is>
+          <t>04 72 00 10 35</t>
+        </is>
+      </c>
       <c r="H395" s="11" t="n"/>
       <c r="I395" s="11" t="n"/>
       <c r="J395" s="11" t="n">
@@ -20601,8 +20749,16 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F397" s="11" t="n"/>
-      <c r="G397" s="11" t="n"/>
+      <c r="F397" s="11" t="inlineStr">
+        <is>
+          <t>41 rue André Sabatier, 69520 Grigny</t>
+        </is>
+      </c>
+      <c r="G397" s="11" t="inlineStr">
+        <is>
+          <t>04 72 24 16 56</t>
+        </is>
+      </c>
       <c r="H397" s="11" t="n"/>
       <c r="I397" s="11" t="n"/>
       <c r="J397" s="11" t="n">
@@ -20638,8 +20794,16 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F398" s="11" t="n"/>
-      <c r="G398" s="11" t="n"/>
+      <c r="F398" s="11" t="inlineStr">
+        <is>
+          <t>15 route de Champagne, 69130 Écully</t>
+        </is>
+      </c>
+      <c r="G398" s="11" t="inlineStr">
+        <is>
+          <t>04 78 33 56 42</t>
+        </is>
+      </c>
       <c r="H398" s="11" t="n"/>
       <c r="I398" s="11" t="n"/>
       <c r="J398" s="11" t="n">
@@ -20675,8 +20839,16 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F399" s="11" t="n"/>
-      <c r="G399" s="11" t="n"/>
+      <c r="F399" s="11" t="inlineStr">
+        <is>
+          <t>19 rue du Capitaine Ferber, 69300 Caluire-et-Cuire</t>
+        </is>
+      </c>
+      <c r="G399" s="11" t="inlineStr">
+        <is>
+          <t>04 78 29 34 98</t>
+        </is>
+      </c>
       <c r="H399" s="11" t="n"/>
       <c r="I399" s="11" t="n"/>
       <c r="J399" s="11" t="n">
@@ -20712,8 +20884,16 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F400" s="11" t="n"/>
-      <c r="G400" s="11" t="n"/>
+      <c r="F400" s="11" t="inlineStr">
+        <is>
+          <t>Place de l'Église, 69670 Vaugneray</t>
+        </is>
+      </c>
+      <c r="G400" s="11" t="inlineStr">
+        <is>
+          <t>04 78 16 80 80</t>
+        </is>
+      </c>
       <c r="H400" s="11" t="n"/>
       <c r="I400" s="11" t="n"/>
       <c r="J400" s="11" t="n">
@@ -20798,9 +20978,21 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F402" s="11" t="n"/>
-      <c r="G402" s="11" t="n"/>
-      <c r="H402" s="11" t="n"/>
+      <c r="F402" s="11" t="inlineStr">
+        <is>
+          <t>34 rue Henri Lebrun, 69330 Meyzieu</t>
+        </is>
+      </c>
+      <c r="G402" s="11" t="inlineStr">
+        <is>
+          <t>04 78 31 09 09</t>
+        </is>
+      </c>
+      <c r="H402" s="11" t="inlineStr">
+        <is>
+          <t>https://www.margueritemeyzieu.com/</t>
+        </is>
+      </c>
       <c r="I402" s="11" t="n"/>
       <c r="J402" s="11" t="n">
         <v>45.7686</v>

--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -17691,8 +17691,16 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F335" s="11" t="n"/>
-      <c r="G335" s="11" t="n"/>
+      <c r="F335" s="11" t="inlineStr">
+        <is>
+          <t>En visioconférence — inscription via France Alzheimer Loire-Atlantique, 8 rue Arsène Leloup, 44100 Nantes</t>
+        </is>
+      </c>
+      <c r="G335" s="11" t="inlineStr">
+        <is>
+          <t>02 40 12 19 19</t>
+        </is>
+      </c>
       <c r="H335" s="11" t="inlineStr">
         <is>
           <t>https://www.francealzheimer.org/loireatlantique/</t>
@@ -18001,7 +18009,11 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F341" s="11" t="n"/>
+      <c r="F341" s="11" t="inlineStr">
+        <is>
+          <t>Pôle Associatif Désiré Colombe, 8 rue Arsène Leloup, 44100 Nantes (inscription obligatoire)</t>
+        </is>
+      </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
           <t>02 40 12 19 19</t>
@@ -18315,7 +18327,11 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F347" s="11" t="n"/>
+      <c r="F347" s="11" t="inlineStr">
+        <is>
+          <t>Pôle Associatif Désiré Colombe, 8 rue Arsène Leloup, 44100 Nantes</t>
+        </is>
+      </c>
       <c r="G347" s="11" t="inlineStr">
         <is>
           <t>02 40 12 19 19</t>
@@ -18364,7 +18380,11 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F348" s="11" t="n"/>
+      <c r="F348" s="11" t="inlineStr">
+        <is>
+          <t>Pôle Associatif Désiré Colombe, 8 rue Arsène Leloup, 44100 Nantes</t>
+        </is>
+      </c>
       <c r="G348" s="11" t="inlineStr">
         <is>
           <t>02 40 12 19 19</t>
@@ -18413,7 +18433,11 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F349" s="11" t="n"/>
+      <c r="F349" s="11" t="inlineStr">
+        <is>
+          <t>Pôle Associatif Désiré Colombe, 8 rue Arsène Leloup, 44100 Nantes</t>
+        </is>
+      </c>
       <c r="G349" s="11" t="inlineStr">
         <is>
           <t>02 40 12 19 19</t>
@@ -18515,7 +18539,11 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F351" s="11" t="n"/>
+      <c r="F351" s="11" t="inlineStr">
+        <is>
+          <t>20 rue Pitre Grenapin, 44600 Saint-Nazaire</t>
+        </is>
+      </c>
       <c r="G351" s="11" t="inlineStr">
         <is>
           <t>07 88 73 61 95</t>
@@ -18829,8 +18857,16 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F357" s="11" t="n"/>
-      <c r="G357" s="11" t="n"/>
+      <c r="F357" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon la plateforme — s'orienter via le CLIC, 10 rue Léopold Cassegrain, 44000 Nantes</t>
+        </is>
+      </c>
+      <c r="G357" s="11" t="inlineStr">
+        <is>
+          <t>02 40 99 29 80 (CLIC de Nantes)</t>
+        </is>
+      </c>
       <c r="H357" s="11" t="inlineStr">
         <is>
           <t>https://www.pays-de-la-loire.ars.sante.fr/en-savoir-plus-sur-laide-aux-aidants</t>
@@ -18874,8 +18910,16 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F358" s="11" t="n"/>
-      <c r="G358" s="11" t="n"/>
+      <c r="F358" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon l'établissement — s'orienter via le CLIC, 10 rue Léopold Cassegrain, 44000 Nantes</t>
+        </is>
+      </c>
+      <c r="G358" s="11" t="inlineStr">
+        <is>
+          <t>02 40 99 29 80 (CLIC de Nantes)</t>
+        </is>
+      </c>
       <c r="H358" s="11" t="inlineStr">
         <is>
           <t>https://www.capgeris.com</t>
@@ -18919,8 +18963,16 @@
           <t>44 — Loire-Atlantique</t>
         </is>
       </c>
-      <c r="F359" s="11" t="n"/>
-      <c r="G359" s="11" t="n"/>
+      <c r="F359" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon l'établissement — s'orienter via le CLIC, 10 rue Léopold Cassegrain, 44000 Nantes</t>
+        </is>
+      </c>
+      <c r="G359" s="11" t="inlineStr">
+        <is>
+          <t>02 40 99 29 80 (CLIC de Nantes)</t>
+        </is>
+      </c>
       <c r="H359" s="11" t="inlineStr">
         <is>
           <t>https://www.capgeris.com</t>
@@ -19186,7 +19238,11 @@
           <t>05 55 45 94 20</t>
         </is>
       </c>
-      <c r="H364" s="11" t="n"/>
+      <c r="H364" s="11" t="inlineStr">
+        <is>
+          <t>https://conseildependance.fr/services/clic/limoges/haute-vienne-87/clic-de-limoges</t>
+        </is>
+      </c>
       <c r="I364" s="11" t="inlineStr">
         <is>
           <t>Information et orientation des aidants.</t>
@@ -19283,7 +19339,11 @@
           <t>19 rue de Rochechouart, 87000 Limoges</t>
         </is>
       </c>
-      <c r="G366" s="11" t="n"/>
+      <c r="G366" s="11" t="inlineStr">
+        <is>
+          <t>05 55 33 96 30 (standard VYV3 Cœur d'Aquitaine)</t>
+        </is>
+      </c>
       <c r="H366" s="11" t="inlineStr">
         <is>
           <t>https://www.vyv3-cda.fr/personnes-agees/accueil-de-jour-rue-de-rochechouart-limoges</t>
@@ -19539,8 +19599,16 @@
           <t>87 — Haute-Vienne</t>
         </is>
       </c>
-      <c r="F371" s="11" t="n"/>
-      <c r="G371" s="11" t="n"/>
+      <c r="F371" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon l'établissement — voir liste ci-dessous</t>
+        </is>
+      </c>
+      <c r="G371" s="11" t="inlineStr">
+        <is>
+          <t>Voir chaque établissement individuellement</t>
+        </is>
+      </c>
       <c r="H371" s="11" t="inlineStr">
         <is>
           <t>https://www.capgeris.com</t>
@@ -19584,9 +19652,21 @@
           <t>87 — Haute-Vienne</t>
         </is>
       </c>
-      <c r="F372" s="11" t="n"/>
-      <c r="G372" s="11" t="n"/>
-      <c r="H372" s="11" t="n"/>
+      <c r="F372" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon l'établissement — voir liste ci-dessous</t>
+        </is>
+      </c>
+      <c r="G372" s="11" t="inlineStr">
+        <is>
+          <t>Voir chaque établissement individuellement</t>
+        </is>
+      </c>
+      <c r="H372" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pour-les-personnes-agees.gouv.fr/annuaire-ehpad-et-maisons-de-retraite/ehpad/haute-vienne-87</t>
+        </is>
+      </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
           <t>Communes concernées : Eymoutiers, Châteauneuf-la-Forêt, Panazol… Unités spécifiques Alzheimer, disponibilité à vérifier au cas par cas.</t>
@@ -19625,9 +19705,21 @@
           <t>87 — Haute-Vienne</t>
         </is>
       </c>
-      <c r="F373" s="11" t="n"/>
-      <c r="G373" s="11" t="n"/>
-      <c r="H373" s="11" t="n"/>
+      <c r="F373" s="11" t="inlineStr">
+        <is>
+          <t>Coordonnées variables selon l'établissement — voir liste ci-dessous</t>
+        </is>
+      </c>
+      <c r="G373" s="11" t="inlineStr">
+        <is>
+          <t>Voir chaque établissement individuellement</t>
+        </is>
+      </c>
+      <c r="H373" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pour-les-personnes-agees.gouv.fr/annuaire-ehpad-et-maisons-de-retraite/ehpad/haute-vienne-87/limoges-87000</t>
+        </is>
+      </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
           <t>EHPAD privé EMEIS, plusieurs EHPAD publics/CCAS, et une USLD (Unité de Soins de Longue Durée) habilitée Alzheimer. Établissements non nommés individuellement, cf. pour-les-personnes-agees.gouv.fr et Capgeris.com.</t>
@@ -19719,7 +19811,11 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F375" s="11" t="n"/>
+      <c r="F375" s="11" t="inlineStr">
+        <is>
+          <t>6 A Cours Bayard, 69002 Lyon (secteur SMD-Interlude, couvrant Lyon 1er, 2e, 4e, 5e)</t>
+        </is>
+      </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
           <t>04 78 42 17 65</t>
@@ -19783,7 +19879,11 @@
           <t>https://www.francealzheimer.org/rhone/</t>
         </is>
       </c>
-      <c r="I376" s="11" t="n"/>
+      <c r="I376" s="11" t="inlineStr">
+        <is>
+          <t>Point d'accueil et d'orientation pour les aidants, au sein du collectif Métropole Aidante. Renseignements auprès de France Alzheimer Rhône (6 place Carnot, 69002 Lyon) ou de la coordination Métropole Aidante au 04 72 69 15 28.</t>
+        </is>
+      </c>
       <c r="J376" s="11" t="n">
         <v>45.758</v>
       </c>
@@ -19870,10 +19970,26 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F378" s="11" t="n"/>
-      <c r="G378" s="11" t="n"/>
-      <c r="H378" s="11" t="n"/>
-      <c r="I378" s="11" t="n"/>
+      <c r="F378" s="11" t="inlineStr">
+        <is>
+          <t>27 rue Hénon, 69004 Lyon</t>
+        </is>
+      </c>
+      <c r="G378" s="11" t="inlineStr">
+        <is>
+          <t>06 95 29 56 40</t>
+        </is>
+      </c>
+      <c r="H378" s="11" t="inlineStr">
+        <is>
+          <t>https://www.smdlyon.fr/</t>
+        </is>
+      </c>
+      <c r="I378" s="11" t="inlineStr">
+        <is>
+          <t>Plateforme d'accompagnement et de répit pour les aidants de personnes atteintes de la maladie d'Alzheimer ou de troubles neuro-évolutifs : accompagnements psychologiques à domicile, ateliers, groupe de parole mensuel. Adhésion associative 16€/an. Contact : plateforme@smdlyon.fr.</t>
+        </is>
+      </c>
       <c r="J378" s="11" t="n">
         <v>45.737</v>
       </c>
@@ -19907,9 +20023,21 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F379" s="11" t="n"/>
-      <c r="G379" s="11" t="n"/>
-      <c r="H379" s="11" t="n"/>
+      <c r="F379" s="11" t="inlineStr">
+        <is>
+          <t>3 Grande Rue, 69110 Sainte-Foy-lès-Lyon</t>
+        </is>
+      </c>
+      <c r="G379" s="11" t="inlineStr">
+        <is>
+          <t>04 78 59 11 64</t>
+        </is>
+      </c>
+      <c r="H379" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ofta.fr/</t>
+        </is>
+      </c>
       <c r="I379" s="11" t="inlineStr">
         <is>
           <t>Animé par une psychologue (« Emilie »).</t>
@@ -19948,9 +20076,21 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F380" s="11" t="n"/>
-      <c r="G380" s="11" t="n"/>
-      <c r="H380" s="11" t="n"/>
+      <c r="F380" s="11" t="inlineStr">
+        <is>
+          <t>124 Place Andrée-Marie Perrin, 69290 Craponne</t>
+        </is>
+      </c>
+      <c r="G380" s="11" t="inlineStr">
+        <is>
+          <t>04 37 22 07 24</t>
+        </is>
+      </c>
+      <c r="H380" s="11" t="inlineStr">
+        <is>
+          <t>https://lesipag.org/</t>
+        </is>
+      </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
           <t>Couvre le secteur de l'Ouest lyonnais.</t>
@@ -20004,7 +20144,11 @@
           <t>https://www.francealzheimer.org/rhone/</t>
         </is>
       </c>
-      <c r="I381" s="11" t="n"/>
+      <c r="I381" s="11" t="inlineStr">
+        <is>
+          <t>Club des aidants ouvert à tous les aidants, activités culturelles et de loisirs, moments de répit. Se réunit deux fois par mois (1er mardi et 3e mercredi, 14h-17h) au 6 place Carnot à Lyon. Inscription au 04 78 42 17 65.</t>
+        </is>
+      </c>
       <c r="J381" s="11" t="n">
         <v>45.7485</v>
       </c>
@@ -20038,9 +20182,21 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F382" s="11" t="n"/>
-      <c r="G382" s="11" t="n"/>
-      <c r="H382" s="11" t="n"/>
+      <c r="F382" s="11" t="inlineStr">
+        <is>
+          <t>Renseignements et lieu exact auprès du secrétariat de France Alzheimer Rhône, 6 place Carnot, 69002 Lyon</t>
+        </is>
+      </c>
+      <c r="G382" s="11" t="inlineStr">
+        <is>
+          <t>04 78 42 17 65</t>
+        </is>
+      </c>
+      <c r="H382" s="11" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org/rhone/</t>
+        </is>
+      </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
           <t>Rendez-vous itinérant sur la métropole lyonnaise.</t>
@@ -20079,7 +20235,11 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F383" s="11" t="n"/>
+      <c r="F383" s="11" t="inlineStr">
+        <is>
+          <t>Renseignements et lieu exact auprès du secrétariat de France Alzheimer Rhône, 6 place Carnot, 69002 Lyon</t>
+        </is>
+      </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
           <t>04 78 42 17 65</t>
@@ -20090,7 +20250,11 @@
           <t>https://www.francealzheimer.org/rhone/</t>
         </is>
       </c>
-      <c r="I383" s="11" t="n"/>
+      <c r="I383" s="11" t="inlineStr">
+        <is>
+          <t>Café Mémoire gratuit et ouvert à tous (malades, aidants, professionnels, grand public), animé par un psychologue et des bénévoles. Inscription/renseignements auprès de France Alzheimer Rhône.</t>
+        </is>
+      </c>
       <c r="J383" s="11" t="n">
         <v>45.4959</v>
       </c>
@@ -20192,7 +20356,11 @@
           <t>https://accueildejour-villalumiere.groupe-acppa.fr/</t>
         </is>
       </c>
-      <c r="I385" s="11" t="n"/>
+      <c r="I385" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique (Lyon 3e), adossé à l'EHPAD Les Cristallines, géré par le Groupe ACPPA, pour personnes atteintes de la maladie d'Alzheimer, de troubles apparentés ou de la maladie de Parkinson. Ouvert du lundi au vendredi de 9h à 17h.</t>
+        </is>
+      </c>
       <c r="J385" s="11" t="n">
         <v>45.755</v>
       </c>
@@ -20241,7 +20409,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I386" s="11" t="n"/>
+      <c r="I386" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique adossé au Pôle Gérontologique Paul-Henri Chapuy, géré par le Groupe ACPPA, pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés vivant à domicile.</t>
+        </is>
+      </c>
       <c r="J386" s="11" t="n">
         <v>45.7775</v>
       </c>
@@ -20290,7 +20462,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I387" s="11" t="n"/>
+      <c r="I387" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique adossé à l'EHPAD La Christinière, géré par le Groupe ACPPA, en plein cœur des Monts du Lyonnais, pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés vivant à domicile.</t>
+        </is>
+      </c>
       <c r="J387" s="11" t="n">
         <v>45.6503</v>
       </c>
@@ -20339,7 +20515,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I388" s="11" t="n"/>
+      <c r="I388" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique adossé à l'EHPAD Castellane, géré par le Groupe ACPPA, pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés vivant à domicile.</t>
+        </is>
+      </c>
       <c r="J388" s="11" t="n">
         <v>45.8106</v>
       </c>
@@ -20388,7 +20568,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I389" s="11" t="n"/>
+      <c r="I389" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique adossé à l'EHPAD Les Alizés, géré par le Groupe ACPPA, pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés vivant à domicile. Espaces lumineux ouverts sur une terrasse.</t>
+        </is>
+      </c>
       <c r="J389" s="11" t="n">
         <v>45.6975</v>
       </c>
@@ -20437,7 +20621,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I390" s="11" t="n"/>
+      <c r="I390" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour thérapeutique de 6 places (« Villa Les Genêts »), adossé à l'EHPAD Les Soleillades, géré par le Groupe ACPPA, pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés vivant à domicile.</t>
+        </is>
+      </c>
       <c r="J390" s="11" t="n">
         <v>45.7364</v>
       </c>
@@ -20486,7 +20674,11 @@
           <t>https://ovpar.fr/accompagnement-et-services/accueil-de-jour/</t>
         </is>
       </c>
-      <c r="I391" s="11" t="n"/>
+      <c r="I391" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 12 places pour personnes de plus de 60 ans atteintes de la maladie d'Alzheimer ou de troubles cognitifs, géré par l'OVPAR (Office villeurbannais des personnes âgées et des retraités). Un transport est proposé. Contact dédié : accueildejour@ovpar.fr / 04 78 26 81 03.</t>
+        </is>
+      </c>
       <c r="J391" s="11" t="n">
         <v>45.7745</v>
       </c>
@@ -20520,10 +20712,26 @@
           <t>69 — Rhône</t>
         </is>
       </c>
-      <c r="F392" s="11" t="n"/>
-      <c r="G392" s="11" t="n"/>
-      <c r="H392" s="11" t="n"/>
-      <c r="I392" s="11" t="n"/>
+      <c r="F392" s="11" t="inlineStr">
+        <is>
+          <t>28 Rue Denfert Rochereau, 69004 Lyon</t>
+        </is>
+      </c>
+      <c r="G392" s="11" t="inlineStr">
+        <is>
+          <t>04 78 28 25 75</t>
+        </is>
+      </c>
+      <c r="H392" s="11" t="inlineStr">
+        <is>
+          <t>https://www.smdlyon.fr/</t>
+        </is>
+      </c>
+      <c r="I392" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour « Interlude » (quartier Confluence, Lyon 2e) et plateforme de répit « Confluence » pour les aidants de personnes atteintes de troubles neuro-évolutifs, gérés par l'association SMD Lyon. Plateforme de répit joignable directement au 06 95 29 56 40 (plateforme@smdlyon.fr).</t>
+        </is>
+      </c>
       <c r="J392" s="11" t="n">
         <v>45.737</v>
       </c>
@@ -20572,7 +20780,11 @@
           <t>https://www.habitat-humanisme.org/ehpads/maison-saint-francois-d-assise/</t>
         </is>
       </c>
-      <c r="I393" s="11" t="n"/>
+      <c r="I393" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 10 places, du lundi au vendredi, au sein d'un EHPAD du réseau Habitat et Humanisme Soin. Équipe dédiée formée à l'accompagnement de la maladie d'Alzheimer.</t>
+        </is>
+      </c>
       <c r="J393" s="11" t="n">
         <v>45.7695</v>
       </c>
@@ -20621,7 +20833,11 @@
           <t>https://residence-jeanvillard.fr/</t>
         </is>
       </c>
-      <c r="I394" s="11" t="n"/>
+      <c r="I394" s="11" t="inlineStr">
+        <is>
+          <t>6 places d'accueil de jour en semaine, au sein d'une résidence intercommunale publique (secteur SIPAG) disposant aussi d'une unité de vie protégée Alzheimer (13 places) et d'une plateforme de répit pour les aidants.</t>
+        </is>
+      </c>
       <c r="J394" s="11" t="n">
         <v>45.7683</v>
       </c>
@@ -20665,8 +20881,16 @@
           <t>04 72 00 10 35</t>
         </is>
       </c>
-      <c r="H395" s="11" t="n"/>
-      <c r="I395" s="11" t="n"/>
+      <c r="H395" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pour-les-personnes-agees.gouv.fr/annuaire-ehpad-et-maisons-de-retraite/ehpad/metropole-de-lyon-69m/neuville-sur-saone-69250/ehpad-de-lhopital-intercommunal-geriatrique-de-neuville/690800032</t>
+        </is>
+      </c>
+      <c r="I395" s="11" t="inlineStr">
+        <is>
+          <t>EHPAD public rattaché à l'hôpital gériatrique intercommunal, avec PASA (pôle d'activités et de soins adaptés) pour les résidents Alzheimer. Pas de site internet propre : fiche officielle via l'annuaire national des EHPAD (lien).</t>
+        </is>
+      </c>
       <c r="J395" s="11" t="n">
         <v>45.8567</v>
       </c>
@@ -20715,7 +20939,11 @@
           <t>https://fleursdautomne.apeb.fr/</t>
         </is>
       </c>
-      <c r="I396" s="11" t="n"/>
+      <c r="I396" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 11 places (pas d'unité Alzheimer dédiée). EHPAD associatif géré par l'APEB (association protestante). Hébergement permanent temporairement fermé aux nouvelles admissions à la date de la recherche : vérifier la disponibilité en accueil de jour directement auprès de l'établissement.</t>
+        </is>
+      </c>
       <c r="J396" s="11" t="n">
         <v>45.7683</v>
       </c>
@@ -20759,8 +20987,16 @@
           <t>04 72 24 16 56</t>
         </is>
       </c>
-      <c r="H397" s="11" t="n"/>
-      <c r="I397" s="11" t="n"/>
+      <c r="H397" s="11" t="inlineStr">
+        <is>
+          <t>https://charme-des-sources.com/fr/</t>
+        </is>
+      </c>
+      <c r="I397" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 8 places au sein de l'EHPAD, qui dispose aussi d'une unité protégée Alzheimer de 14 places. Ouvert du lundi au vendredi.</t>
+        </is>
+      </c>
       <c r="J397" s="11" t="n">
         <v>45.6167</v>
       </c>
@@ -20804,8 +21040,16 @@
           <t>04 78 33 56 42</t>
         </is>
       </c>
-      <c r="H398" s="11" t="n"/>
-      <c r="I398" s="11" t="n"/>
+      <c r="H398" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ecully.fr/a-tout-age/seniors/structures-d-hebergement-368.html</t>
+        </is>
+      </c>
+      <c r="I398" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour Alzheimer de 12 places, du lundi au vendredi 9h-17h (1 à 3 jours/semaine). Structure municipale gérée par le CCAS d'Écully : psychologue et aides-soignants formés présents au quotidien.</t>
+        </is>
+      </c>
       <c r="J398" s="11" t="n">
         <v>45.7767</v>
       </c>
@@ -20849,8 +21093,16 @@
           <t>04 78 29 34 98</t>
         </is>
       </c>
-      <c r="H399" s="11" t="n"/>
-      <c r="I399" s="11" t="n"/>
+      <c r="H399" s="11" t="inlineStr">
+        <is>
+          <t>mailto:accueil@ehpadmanoir.com</t>
+        </is>
+      </c>
+      <c r="I399" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 12 places (« La Villa »), rattaché à l'EHPAD Le Manoir, géré par l'association Foyer des Tilleuls. Pas de site internet dédié : contact par téléphone ou e-mail.</t>
+        </is>
+      </c>
       <c r="J399" s="11" t="n">
         <v>45.7907</v>
       </c>
@@ -20894,8 +21146,16 @@
           <t>04 78 16 80 80</t>
         </is>
       </c>
-      <c r="H400" s="11" t="n"/>
-      <c r="I400" s="11" t="n"/>
+      <c r="H400" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pour-les-personnes-agees.gouv.fr/annuaire-ehpad-et-maisons-de-retraite/ehpad/rhone-69d/vaugneray-69670/ehpad-saint-joseph/690793583</t>
+        </is>
+      </c>
+      <c r="I400" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 12 places avec PASA (pôle d'activités et de soins adaptés) sur place. Pas de site internet propre : fiche officielle disponible via l'annuaire national des EHPAD (lien).</t>
+        </is>
+      </c>
       <c r="J400" s="11" t="n">
         <v>45.7397</v>
       </c>
@@ -20944,7 +21204,11 @@
           <t>https://www.groupe-acppa.fr</t>
         </is>
       </c>
-      <c r="I401" s="11" t="n"/>
+      <c r="I401" s="11" t="inlineStr">
+        <is>
+          <t>EHPAD du Groupe ACPPA proposant un accueil de jour thérapeutique dédié, la Villa Van Gogh (voir fiche séparée), pour les personnes atteintes de la maladie d'Alzheimer ou de troubles apparentés.</t>
+        </is>
+      </c>
       <c r="J401" s="11" t="n">
         <v>45.6975</v>
       </c>
@@ -20993,7 +21257,11 @@
           <t>https://www.margueritemeyzieu.com/</t>
         </is>
       </c>
-      <c r="I402" s="11" t="n"/>
+      <c r="I402" s="11" t="inlineStr">
+        <is>
+          <t>Accueil de jour de 6 places au sein de l'unité Alzheimer, dans un grand parc arboré. Contactez directement l'établissement pour les modalités d'inscription et les tarifs.</t>
+        </is>
+      </c>
       <c r="J402" s="11" t="n">
         <v>45.7686</v>
       </c>
